--- a/output/Data and Chart Outputs/taiwan_reservoirs_daily.xlsx
+++ b/output/Data and Chart Outputs/taiwan_reservoirs_daily.xlsx
@@ -15,13 +15,14 @@
     <sheet name="Water year - WRA 20201" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Water year - WRA 20502" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Water year - WRA 20101" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Water year - WRA 20509" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Water year - WRA 10405" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Water year - WRA 10501" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Water year - WRA 31201" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Daily storage" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Daily level" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Reservoirs" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Water year - WRA 30503" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Water year - WRA 20509" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Water year - WRA 10405" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Water year - WRA 10501" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Water year - WRA 31201" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Daily storage" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Daily level" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Reservoirs" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -204,12 +205,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$3</f>
+              <f>'Chart'!$I$2:$I$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$3</f>
+              <f>'Chart'!$B$2:$B$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -240,12 +241,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$3</f>
+              <f>'Chart'!$I$2:$I$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$3</f>
+              <f>'Chart'!$C$2:$C$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -276,12 +277,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$3</f>
+              <f>'Chart'!$I$2:$I$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$3</f>
+              <f>'Chart'!$D$2:$D$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -312,12 +313,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$3</f>
+              <f>'Chart'!$I$2:$I$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$3</f>
+              <f>'Chart'!$E$2:$E$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -348,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$3</f>
+              <f>'Chart'!$I$2:$I$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$3</f>
+              <f>'Chart'!$F$2:$F$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -384,12 +385,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$3</f>
+              <f>'Chart'!$I$2:$I$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$3</f>
+              <f>'Chart'!$G$2:$G$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -420,12 +421,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$3</f>
+              <f>'Chart'!$I$2:$I$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$3</f>
+              <f>'Chart'!$H$2:$H$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -525,7 +526,278 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 10501 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-10</a:t>
+              <a:t>WRA 10405 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-11</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <areaChart>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v> </v>
+          </tx>
+          <spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Water year - WRA 10405'!$H$2:$H$366</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Water year - WRA 10405'!$B$2:$B$366</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>5-year range (2021/22-2025/26)</v>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="AFC6D9"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Water year - WRA 10405'!$H$2:$H$366</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Water year - WRA 10405'!$C$2:$C$366</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </areaChart>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Water year - WRA 10405'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="6E6E6E"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Water year - WRA 10405'!$H$2:$H$366</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Water year - WRA 10405'!$E$2:$E$366</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Water year - WRA 10405'!F1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Water year - WRA 10405'!$H$2:$H$366</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Water year - WRA 10405'!$F$2:$F$366</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Water year - WRA 10405'!G1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="38100">
+              <a:solidFill>
+                <a:srgbClr val="0B3A66"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Water year - WRA 10405'!$H$2:$H$366</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Water year - WRA 10405'!$G$2:$G$366</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="3330"/>
+          <min val="3300"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>million m3</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="0"/>
+        </title>
+        <numFmt formatCode="0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+        <majorUnit val="5"/>
+      </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <overlay val="0"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>WRA 10501 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-11</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -732,8 +1004,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2888"/>
-          <min val="2872"/>
+          <max val="2890"/>
+          <min val="2860"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -758,7 +1030,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <majorUnit val="2"/>
+        <majorUnit val="5"/>
       </valAx>
       <spPr>
         <a:ln>
@@ -783,7 +1055,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -796,7 +1068,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 31201 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-10</a:t>
+              <a:t>WRA 31201 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-11</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1004,7 +1276,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="2420"/>
-          <min val="2418"/>
+          <min val="2414"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -1029,7 +1301,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <majorUnit val="0.5"/>
+        <majorUnit val="1"/>
       </valAx>
       <spPr>
         <a:ln>
@@ -1067,7 +1339,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 30502 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-10</a:t>
+              <a:t>WRA 30502 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-11</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1274,8 +1546,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46100"/>
-          <min val="45600"/>
+          <max val="46200"/>
+          <min val="45200"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -1300,7 +1572,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <majorUnit val="100"/>
+        <majorUnit val="200"/>
       </valAx>
       <spPr>
         <a:ln>
@@ -1338,7 +1610,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 10205 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-10</a:t>
+              <a:t>WRA 10205 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-11</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1546,7 +1818,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="27450"/>
-          <min val="27380"/>
+          <min val="27300"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -1571,7 +1843,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <majorUnit val="10"/>
+        <majorUnit val="25"/>
       </valAx>
       <spPr>
         <a:ln>
@@ -1609,7 +1881,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 10201 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-10</a:t>
+              <a:t>WRA 10201 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-11</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1816,8 +2088,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="19960"/>
-          <min val="19900"/>
+          <max val="19975"/>
+          <min val="19800"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -1842,7 +2114,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <majorUnit val="10"/>
+        <majorUnit val="25"/>
       </valAx>
       <spPr>
         <a:ln>
@@ -1880,7 +2152,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 20201 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-10</a:t>
+              <a:t>WRA 20201 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-11</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2151,7 +2423,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 20502 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-10</a:t>
+              <a:t>WRA 20502 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-11</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2422,7 +2694,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 20101 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-10</a:t>
+              <a:t>WRA 20101 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-11</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2630,7 +2902,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="11520"/>
-          <min val="11508"/>
+          <min val="11500"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -2655,7 +2927,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <majorUnit val="2"/>
+        <majorUnit val="2.5"/>
       </valAx>
       <spPr>
         <a:ln>
@@ -2693,7 +2965,278 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 20509 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-10</a:t>
+              <a:t>WRA 30503 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-11</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <areaChart>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v> </v>
+          </tx>
+          <spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Water year - WRA 30503'!$H$2:$H$366</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Water year - WRA 30503'!$B$2:$B$366</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>5-year range (2021/22-2025/26)</v>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="AFC6D9"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Water year - WRA 30503'!$H$2:$H$366</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Water year - WRA 30503'!$C$2:$C$366</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </areaChart>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Water year - WRA 30503'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="6E6E6E"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Water year - WRA 30503'!$H$2:$H$366</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Water year - WRA 30503'!$E$2:$E$366</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Water year - WRA 30503'!F1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Water year - WRA 30503'!$H$2:$H$366</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Water year - WRA 30503'!$F$2:$F$366</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Water year - WRA 30503'!G1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="38100">
+              <a:solidFill>
+                <a:srgbClr val="0B3A66"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Water year - WRA 30503'!$H$2:$H$366</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Water year - WRA 30503'!$G$2:$G$366</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="8095"/>
+          <min val="8070"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>million m3</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="0"/>
+        </title>
+        <numFmt formatCode="0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+        <majorUnit val="5"/>
+      </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <overlay val="0"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>WRA 20509 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-11</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2951,277 +3494,6 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 10405 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-10</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-    </title>
-    <plotArea>
-      <areaChart>
-        <grouping val="stacked"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <v> </v>
-          </tx>
-          <spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Water year - WRA 10405'!$H$2:$H$366</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Water year - WRA 10405'!$B$2:$B$366</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <v>5-year range (2021/22-2025/26)</v>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="AFC6D9"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Water year - WRA 10405'!$H$2:$H$366</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Water year - WRA 10405'!$C$2:$C$366</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </areaChart>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
-              <f>'Water year - WRA 10405'!E1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="6E6E6E"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Water year - WRA 10405'!$H$2:$H$366</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Water year - WRA 10405'!$E$2:$E$366</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="3"/>
-          <order val="3"/>
-          <tx>
-            <strRef>
-              <f>'Water year - WRA 10405'!F1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="2A78D6"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Water year - WRA 10405'!$H$2:$H$366</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Water year - WRA 10405'!$F$2:$F$366</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="4"/>
-          <order val="4"/>
-          <tx>
-            <strRef>
-              <f>'Water year - WRA 10405'!G1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="38100">
-              <a:solidFill>
-                <a:srgbClr val="0B3A66"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Water year - WRA 10405'!$H$2:$H$366</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Water year - WRA 10405'!$G$2:$G$366</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="low"/>
-        <txPr>
-          <a:bodyPr rot="-2700000" vert="horz"/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr/>
-          </a:p>
-        </txPr>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-        <tickLblSkip val="1"/>
-        <tickMarkSkip val="1"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-          <max val="3330"/>
-          <min val="3318"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>million m3</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-          <overlay val="0"/>
-        </title>
-        <numFmt formatCode="0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-        <majorUnit val="2"/>
-      </valAx>
-      <spPr>
-        <a:ln>
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </plotArea>
-    <legend>
-      <legendPos val="b"/>
-      <overlay val="0"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:ln>
-      <a:noFill/>
-      <a:prstDash val="solid"/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -3277,6 +3549,33 @@
 </file>
 
 <file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9360000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -3998,7 +4297,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3329.2</v>
+        <v>5034.81</v>
       </c>
     </row>
     <row r="11">
@@ -4008,7 +4307,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3319.18</v>
+        <v>5032.74</v>
       </c>
     </row>
     <row r="12">
@@ -4016,6 +4315,9 @@
         <is>
           <t>11-Oct</t>
         </is>
+      </c>
+      <c r="G12" t="n">
+        <v>5032.74</v>
       </c>
     </row>
     <row r="13">
@@ -6685,7 +6987,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2887.18</v>
+        <v>3329.2</v>
       </c>
     </row>
     <row r="11">
@@ -6695,7 +6997,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2873.37</v>
+        <v>3319.18</v>
       </c>
     </row>
     <row r="12">
@@ -6703,6 +7005,9 @@
         <is>
           <t>11-Oct</t>
         </is>
+      </c>
+      <c r="G12" t="n">
+        <v>3304.5</v>
       </c>
     </row>
     <row r="13">
@@ -9372,7 +9677,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2420</v>
+        <v>2887.18</v>
       </c>
     </row>
     <row r="11">
@@ -9382,7 +9687,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2418</v>
+        <v>2873.37</v>
       </c>
     </row>
     <row r="12">
@@ -9390,6 +9695,9 @@
         <is>
           <t>11-Oct</t>
         </is>
+      </c>
+      <c r="G12" t="n">
+        <v>2863.04</v>
       </c>
     </row>
     <row r="13">
@@ -11937,421 +12245,2687 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH3"/>
+  <dimension ref="A1:H366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B1" t="n">
-        <v>10201</v>
-      </c>
-      <c r="C1" t="n">
-        <v>10203</v>
-      </c>
-      <c r="D1" t="n">
-        <v>10204</v>
-      </c>
-      <c r="E1" t="n">
-        <v>10205</v>
-      </c>
-      <c r="F1" t="n">
-        <v>10211</v>
-      </c>
-      <c r="G1" t="n">
-        <v>10212</v>
-      </c>
-      <c r="H1" t="n">
-        <v>10401</v>
-      </c>
-      <c r="I1" t="n">
-        <v>10405</v>
-      </c>
-      <c r="J1" t="n">
-        <v>10501</v>
-      </c>
-      <c r="K1" t="n">
-        <v>10601</v>
-      </c>
-      <c r="L1" t="n">
-        <v>10802</v>
-      </c>
-      <c r="M1" t="n">
-        <v>20101</v>
-      </c>
-      <c r="N1" t="n">
-        <v>20201</v>
-      </c>
-      <c r="O1" t="n">
-        <v>20202</v>
-      </c>
-      <c r="P1" t="n">
-        <v>20501</v>
-      </c>
-      <c r="Q1" t="n">
-        <v>20502</v>
-      </c>
-      <c r="R1" t="n">
-        <v>20503</v>
-      </c>
-      <c r="S1" t="n">
-        <v>20509</v>
-      </c>
-      <c r="T1" t="n">
-        <v>30301</v>
-      </c>
-      <c r="U1" t="n">
-        <v>30302</v>
-      </c>
-      <c r="V1" t="n">
-        <v>30401</v>
-      </c>
-      <c r="W1" t="n">
-        <v>30502</v>
-      </c>
-      <c r="X1" t="n">
-        <v>30503</v>
-      </c>
-      <c r="Y1" t="n">
-        <v>30504</v>
-      </c>
-      <c r="Z1" t="n">
-        <v>30802</v>
-      </c>
-      <c r="AA1" t="n">
-        <v>30901</v>
-      </c>
-      <c r="AB1" t="n">
-        <v>31002</v>
-      </c>
-      <c r="AC1" t="n">
-        <v>31201</v>
-      </c>
-      <c r="AD1" t="n">
-        <v>31301</v>
-      </c>
-      <c r="AE1" t="n">
-        <v>50102</v>
-      </c>
-      <c r="AF1" t="n">
-        <v>50103</v>
-      </c>
-      <c r="AG1" t="n">
-        <v>50104</v>
-      </c>
-      <c r="AH1" t="n">
-        <v>50105</v>
-      </c>
-      <c r="AI1" t="n">
-        <v>50106</v>
-      </c>
-      <c r="AJ1" t="n">
-        <v>50108</v>
-      </c>
-      <c r="AK1" t="n">
-        <v>50109</v>
-      </c>
-      <c r="AL1" t="n">
-        <v>50201</v>
-      </c>
-      <c r="AM1" t="n">
-        <v>50202</v>
-      </c>
-      <c r="AN1" t="n">
-        <v>50203</v>
-      </c>
-      <c r="AO1" t="n">
-        <v>50204</v>
-      </c>
-      <c r="AP1" t="n">
-        <v>50205</v>
-      </c>
-      <c r="AQ1" t="n">
-        <v>50206</v>
-      </c>
-      <c r="AR1" t="n">
-        <v>50207</v>
-      </c>
-      <c r="AS1" t="n">
-        <v>50208</v>
-      </c>
-      <c r="AT1" t="n">
-        <v>50209</v>
-      </c>
-      <c r="AU1" t="n">
-        <v>50210</v>
-      </c>
-      <c r="AV1" t="n">
-        <v>50212</v>
-      </c>
-      <c r="AW1" t="n">
-        <v>50213</v>
-      </c>
-      <c r="AX1" t="n">
-        <v>50214</v>
-      </c>
-      <c r="AY1" t="n">
-        <v>50301</v>
-      </c>
-      <c r="AZ1" t="n">
-        <v>50302</v>
-      </c>
-      <c r="BA1" t="n">
-        <v>50303</v>
-      </c>
-      <c r="BB1" t="n">
-        <v>50304</v>
-      </c>
-      <c r="BC1" t="n">
-        <v>50305</v>
-      </c>
-      <c r="BD1" t="n">
-        <v>50306</v>
-      </c>
-      <c r="BE1" t="n">
-        <v>50307</v>
-      </c>
-      <c r="BF1" t="n">
-        <v>50308</v>
-      </c>
-      <c r="BG1" t="n">
-        <v>50309</v>
-      </c>
-      <c r="BH1" t="n">
-        <v>50310</v>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>5Y min</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>5Y range (max-min)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>5Y max</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>5Y average</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>WY 2025/26</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>WY 2026/27</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Axis label</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n">
-        <v>46304</v>
-      </c>
-      <c r="B2" t="n">
-        <v>19953.65</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27448.98</v>
-      </c>
-      <c r="H2" t="n">
-        <v>494.91</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3329.2</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2887.18</v>
-      </c>
-      <c r="K2" t="n">
-        <v>897.6799999999999</v>
-      </c>
-      <c r="M2" t="n">
-        <v>11518.41</v>
-      </c>
-      <c r="N2" t="n">
-        <v>17879.38</v>
-      </c>
-      <c r="O2" t="n">
-        <v>74.27</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1637.13</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>12078.99</v>
-      </c>
-      <c r="R2" t="n">
-        <v>67.83</v>
-      </c>
-      <c r="S2" t="n">
-        <v>5034.81</v>
-      </c>
-      <c r="W2" t="n">
-        <v>46042</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1920</v>
-      </c>
-      <c r="AC2" t="n">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>01-Oct</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>01-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>02-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>03-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>04-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>05-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>06-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>07-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>08-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>09-Oct</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
         <v>2420</v>
       </c>
-      <c r="AY2" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>11.42</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>6.91</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>27.63</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="n">
-        <v>46305</v>
-      </c>
-      <c r="B3" t="n">
-        <v>19902.41</v>
-      </c>
-      <c r="C3" t="n">
-        <v>36.66</v>
-      </c>
-      <c r="D3" t="n">
-        <v>859.59</v>
-      </c>
-      <c r="E3" t="n">
-        <v>27384.03</v>
-      </c>
-      <c r="F3" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="G3" t="n">
-        <v>149.63</v>
-      </c>
-      <c r="H3" t="n">
-        <v>491.97</v>
-      </c>
-      <c r="I3" t="n">
-        <v>3319.18</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2873.37</v>
-      </c>
-      <c r="K3" t="n">
-        <v>881.5</v>
-      </c>
-      <c r="M3" t="n">
-        <v>11509.78</v>
-      </c>
-      <c r="N3" t="n">
-        <v>17883.55</v>
-      </c>
-      <c r="O3" t="n">
-        <v>74.27</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1627.37</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>11777.04</v>
-      </c>
-      <c r="R3" t="n">
-        <v>64.73999999999999</v>
-      </c>
-      <c r="S3" t="n">
-        <v>5032.74</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2242.67</v>
-      </c>
-      <c r="U3" t="n">
-        <v>865.14</v>
-      </c>
-      <c r="V3" t="n">
-        <v>984</v>
-      </c>
-      <c r="W3" t="n">
-        <v>45683</v>
-      </c>
-      <c r="X3" t="n">
-        <v>8074.37</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>55.09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1917</v>
-      </c>
-      <c r="AC3" t="n">
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
         <v>2418</v>
       </c>
-      <c r="AD3" t="n">
-        <v>115.89</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>52.05</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>27.64</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>36.39</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>145.02</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>37.43</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>18.87</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>19.02</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>35.96</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>23.65</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>40.98</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>7.66</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>29.51</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>38.11</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>29.32</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>14.43</v>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>11-Oct</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>2414</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>14-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>15-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>16-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>17-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>18-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>19-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>21-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>22-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>23-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>24-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>25-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>26-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>27-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>28-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>29-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>30-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>31-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>01-Nov</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>01-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>02-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>03-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>04-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>05-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>06-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>07-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>08-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>09-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>10-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>11-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>12-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>13-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>14-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>15-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>16-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>17-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>18-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>19-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>21-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>22-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>23-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>24-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>25-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>26-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>27-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>28-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>29-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>30-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>01-Dec</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>01-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>02-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>03-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>04-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>05-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>06-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>07-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>08-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>09-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>10-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>11-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>12-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>13-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>14-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>15-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>16-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>17-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>18-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>19-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>20-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>21-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>22-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>23-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>24-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>25-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>26-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>27-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>28-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>29-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>30-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>31-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>01-Jan</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>01-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>02-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>03-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>04-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>05-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>06-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>07-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>08-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>09-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>10-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>11-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>12-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>13-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>14-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>15-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>16-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>17-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>18-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>19-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>20-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>21-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>22-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>23-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>24-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>25-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>26-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>27-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>28-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>29-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>30-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>31-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>01-Feb</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>01-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>02-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>03-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>04-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>05-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>06-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>07-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>08-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>09-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>10-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>11-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>12-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>13-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>14-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>15-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>16-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>17-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>18-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>19-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>20-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>21-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>22-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>23-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>24-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>25-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>26-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>27-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>28-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>01-Mar</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>01-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>02-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>03-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>04-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>05-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>06-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>07-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>08-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>09-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>10-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>11-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>12-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>13-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>14-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>15-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>16-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>17-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>18-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>19-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>20-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>21-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>22-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>23-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>24-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>25-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>26-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>27-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>28-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>29-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>30-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>31-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>01-Apr</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>01-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>02-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>03-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>04-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>05-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>06-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>07-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>08-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>09-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>10-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>11-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>12-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>13-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>14-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>15-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>16-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>17-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>18-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>19-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>20-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>21-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>22-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>23-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>24-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>25-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>26-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>27-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>28-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>29-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>30-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>01-May</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>01-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>02-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>03-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>04-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>05-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>06-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>07-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>08-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>09-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>10-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>11-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>12-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>13-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>14-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>15-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>16-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>17-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>18-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>19-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>20-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>21-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>22-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>23-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>24-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>25-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>26-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>27-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>28-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>29-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>30-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>31-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>01-Jun</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>01-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>02-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>03-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>04-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>05-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>06-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>07-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>08-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>09-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>10-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>11-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>12-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>13-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>14-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>15-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>16-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>17-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>18-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>19-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>20-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>21-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>22-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>23-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>24-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>25-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>26-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>27-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>28-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>29-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>30-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>01-Jul</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>01-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>02-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>03-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>04-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>05-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>06-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>07-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>08-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>09-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>10-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>11-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>12-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>13-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>14-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>15-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>16-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>17-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>18-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>19-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>20-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>21-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>22-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>23-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>24-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>25-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>26-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>27-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>28-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>29-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>30-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>31-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>01-Aug</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>01-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>02-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>03-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>04-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>05-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>06-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>07-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>08-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>09-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>10-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>11-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>12-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>13-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>14-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>15-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>16-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>17-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>18-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>19-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>20-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>21-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>22-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>23-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>24-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>25-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>26-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>27-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>28-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>29-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>30-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>31-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>01-Sep</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>01-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>02-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>03-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>04-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>05-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>06-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>07-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>08-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>09-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>10-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>11-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>12-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>13-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>14-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>15-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>16-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>17-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>18-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>19-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>20-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>21-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>22-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>23-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>24-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>25-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>26-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>27-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>28-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>29-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>30-Sep</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -12361,7 +14935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH3"/>
+  <dimension ref="A1:BI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12434,117 +15008,120 @@
         <v>30401</v>
       </c>
       <c r="W1" t="n">
+        <v>30501</v>
+      </c>
+      <c r="X1" t="n">
         <v>30502</v>
       </c>
-      <c r="X1" t="n">
+      <c r="Y1" t="n">
         <v>30503</v>
       </c>
-      <c r="Y1" t="n">
+      <c r="Z1" t="n">
         <v>30504</v>
       </c>
-      <c r="Z1" t="n">
+      <c r="AA1" t="n">
         <v>30802</v>
       </c>
-      <c r="AA1" t="n">
+      <c r="AB1" t="n">
         <v>30901</v>
       </c>
-      <c r="AB1" t="n">
+      <c r="AC1" t="n">
         <v>31002</v>
       </c>
-      <c r="AC1" t="n">
+      <c r="AD1" t="n">
         <v>31201</v>
       </c>
-      <c r="AD1" t="n">
+      <c r="AE1" t="n">
         <v>31301</v>
       </c>
-      <c r="AE1" t="n">
+      <c r="AF1" t="n">
         <v>50102</v>
       </c>
-      <c r="AF1" t="n">
+      <c r="AG1" t="n">
         <v>50103</v>
       </c>
-      <c r="AG1" t="n">
+      <c r="AH1" t="n">
         <v>50104</v>
       </c>
-      <c r="AH1" t="n">
+      <c r="AI1" t="n">
         <v>50105</v>
       </c>
-      <c r="AI1" t="n">
+      <c r="AJ1" t="n">
         <v>50106</v>
       </c>
-      <c r="AJ1" t="n">
+      <c r="AK1" t="n">
         <v>50108</v>
       </c>
-      <c r="AK1" t="n">
+      <c r="AL1" t="n">
         <v>50109</v>
       </c>
-      <c r="AL1" t="n">
+      <c r="AM1" t="n">
         <v>50201</v>
       </c>
-      <c r="AM1" t="n">
+      <c r="AN1" t="n">
         <v>50202</v>
       </c>
-      <c r="AN1" t="n">
+      <c r="AO1" t="n">
         <v>50203</v>
       </c>
-      <c r="AO1" t="n">
+      <c r="AP1" t="n">
         <v>50204</v>
       </c>
-      <c r="AP1" t="n">
+      <c r="AQ1" t="n">
         <v>50205</v>
       </c>
-      <c r="AQ1" t="n">
+      <c r="AR1" t="n">
         <v>50206</v>
       </c>
-      <c r="AR1" t="n">
+      <c r="AS1" t="n">
         <v>50207</v>
       </c>
-      <c r="AS1" t="n">
+      <c r="AT1" t="n">
         <v>50208</v>
       </c>
-      <c r="AT1" t="n">
+      <c r="AU1" t="n">
         <v>50209</v>
       </c>
-      <c r="AU1" t="n">
+      <c r="AV1" t="n">
         <v>50210</v>
       </c>
-      <c r="AV1" t="n">
+      <c r="AW1" t="n">
         <v>50212</v>
       </c>
-      <c r="AW1" t="n">
+      <c r="AX1" t="n">
         <v>50213</v>
       </c>
-      <c r="AX1" t="n">
+      <c r="AY1" t="n">
         <v>50214</v>
       </c>
-      <c r="AY1" t="n">
+      <c r="AZ1" t="n">
         <v>50301</v>
       </c>
-      <c r="AZ1" t="n">
+      <c r="BA1" t="n">
         <v>50302</v>
       </c>
-      <c r="BA1" t="n">
+      <c r="BB1" t="n">
         <v>50303</v>
       </c>
-      <c r="BB1" t="n">
+      <c r="BC1" t="n">
         <v>50304</v>
       </c>
-      <c r="BC1" t="n">
+      <c r="BD1" t="n">
         <v>50305</v>
       </c>
-      <c r="BD1" t="n">
+      <c r="BE1" t="n">
         <v>50306</v>
       </c>
-      <c r="BE1" t="n">
+      <c r="BF1" t="n">
         <v>50307</v>
       </c>
-      <c r="BF1" t="n">
+      <c r="BG1" t="n">
         <v>50308</v>
       </c>
-      <c r="BG1" t="n">
+      <c r="BH1" t="n">
         <v>50309</v>
       </c>
-      <c r="BH1" t="n">
+      <c r="BI1" t="n">
         <v>50310</v>
       </c>
     </row>
@@ -12553,88 +15130,82 @@
         <v>46304</v>
       </c>
       <c r="B2" t="n">
-        <v>244.33</v>
+        <v>19953.65</v>
       </c>
       <c r="E2" t="n">
-        <v>159.01</v>
+        <v>27448.98</v>
       </c>
       <c r="H2" t="n">
-        <v>141.5</v>
+        <v>494.91</v>
       </c>
       <c r="I2" t="n">
-        <v>151</v>
+        <v>3329.2</v>
       </c>
       <c r="J2" t="n">
-        <v>84.36</v>
+        <v>2887.18</v>
       </c>
       <c r="K2" t="n">
-        <v>58.49</v>
+        <v>897.6799999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>299.93</v>
+        <v>11518.41</v>
       </c>
       <c r="N2" t="n">
-        <v>1407.34</v>
+        <v>17879.38</v>
       </c>
       <c r="O2" t="n">
-        <v>273.63</v>
+        <v>74.27</v>
       </c>
       <c r="P2" t="n">
-        <v>1001.34</v>
+        <v>1637.13</v>
       </c>
       <c r="Q2" t="n">
-        <v>747.4</v>
+        <v>12078.99</v>
       </c>
       <c r="R2" t="n">
-        <v>209.56</v>
+        <v>67.83</v>
       </c>
       <c r="S2" t="n">
-        <v>211.47</v>
-      </c>
-      <c r="W2" t="n">
-        <v>228.58</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>38.41</v>
+        <v>5034.81</v>
+      </c>
+      <c r="X2" t="n">
+        <v>46042</v>
       </c>
       <c r="AA2" t="n">
-        <v>16.31</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>246.03</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>140.66</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>7.93</v>
+        <v>1920</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2420</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.21</v>
+        <v>2.93</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.86</v>
+        <v>0.42</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.6</v>
+        <v>0.12</v>
       </c>
       <c r="BC2" t="n">
-        <v>16.48</v>
+        <v>1.54</v>
       </c>
       <c r="BD2" t="n">
-        <v>13.33</v>
+        <v>2.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.73</v>
+        <v>1.47</v>
       </c>
       <c r="BF2" t="n">
-        <v>17.51</v>
+        <v>0.34</v>
       </c>
       <c r="BG2" t="n">
-        <v>17.16</v>
+        <v>11.42</v>
       </c>
       <c r="BH2" t="n">
-        <v>12.66</v>
+        <v>6.91</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>27.63</v>
       </c>
     </row>
     <row r="3">
@@ -12642,151 +15213,288 @@
         <v>46305</v>
       </c>
       <c r="B3" t="n">
-        <v>244.27</v>
+        <v>19902.41</v>
       </c>
       <c r="C3" t="n">
-        <v>71.95</v>
+        <v>36.66</v>
       </c>
       <c r="D3" t="n">
-        <v>83.23999999999999</v>
+        <v>859.59</v>
       </c>
       <c r="E3" t="n">
-        <v>158.93</v>
+        <v>27384.03</v>
       </c>
       <c r="F3" t="n">
-        <v>22.19</v>
+        <v>61.5</v>
       </c>
       <c r="G3" t="n">
-        <v>44.34</v>
+        <v>149.63</v>
       </c>
       <c r="H3" t="n">
-        <v>141.45</v>
+        <v>491.97</v>
       </c>
       <c r="I3" t="n">
-        <v>150.94</v>
+        <v>3319.18</v>
       </c>
       <c r="J3" t="n">
-        <v>84.28</v>
+        <v>2873.37</v>
       </c>
       <c r="K3" t="n">
-        <v>58.37</v>
-      </c>
-      <c r="L3" t="n">
-        <v>4.99</v>
+        <v>881.5</v>
       </c>
       <c r="M3" t="n">
-        <v>299.91</v>
+        <v>11509.78</v>
       </c>
       <c r="N3" t="n">
-        <v>1407.35</v>
+        <v>17883.55</v>
       </c>
       <c r="O3" t="n">
-        <v>273.63</v>
+        <v>74.27</v>
       </c>
       <c r="P3" t="n">
-        <v>1001.29</v>
+        <v>1627.37</v>
       </c>
       <c r="Q3" t="n">
-        <v>747.02</v>
+        <v>11777.04</v>
       </c>
       <c r="R3" t="n">
-        <v>209.49</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>211.46</v>
+        <v>5032.74</v>
       </c>
       <c r="T3" t="n">
-        <v>104.05</v>
+        <v>2242.67</v>
       </c>
       <c r="U3" t="n">
-        <v>74.69</v>
+        <v>865.14</v>
       </c>
       <c r="V3" t="n">
-        <v>106.42</v>
-      </c>
-      <c r="W3" t="n">
-        <v>228.38</v>
+        <v>984</v>
       </c>
       <c r="X3" t="n">
-        <v>179.77</v>
+        <v>45683</v>
       </c>
       <c r="Y3" t="n">
-        <v>138.96</v>
+        <v>8074.37</v>
       </c>
       <c r="Z3" t="n">
-        <v>38.4</v>
+        <v>55.09</v>
       </c>
       <c r="AA3" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>246.03</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>140.64</v>
+        <v>1917</v>
       </c>
       <c r="AD3" t="n">
-        <v>8.779999999999999</v>
+        <v>2418</v>
       </c>
       <c r="AE3" t="n">
-        <v>9.41</v>
+        <v>115.89</v>
       </c>
       <c r="AF3" t="n">
-        <v>5.55</v>
+        <v>52.05</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.86</v>
+        <v>27.64</v>
       </c>
       <c r="AH3" t="n">
-        <v>12.4</v>
+        <v>36.39</v>
       </c>
       <c r="AI3" t="n">
-        <v>23.9</v>
+        <v>23.4</v>
       </c>
       <c r="AJ3" t="n">
-        <v>7.4</v>
+        <v>21.9</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.8</v>
+        <v>4.45</v>
       </c>
       <c r="AL3" t="n">
-        <v>18.27</v>
+        <v>0.39</v>
       </c>
       <c r="AM3" t="n">
-        <v>5.66</v>
+        <v>145.02</v>
       </c>
       <c r="AN3" t="n">
-        <v>30.49</v>
+        <v>37.43</v>
       </c>
       <c r="AO3" t="n">
-        <v>18.17</v>
+        <v>18.87</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.65</v>
+        <v>19.02</v>
       </c>
       <c r="AQ3" t="n">
-        <v>30.59</v>
+        <v>35.96</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.52</v>
+        <v>23.65</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.220000000000001</v>
+        <v>40.98</v>
       </c>
       <c r="AT3" t="n">
-        <v>12.27</v>
+        <v>5.07</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.37</v>
+        <v>7.66</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.69</v>
+        <v>29.51</v>
       </c>
       <c r="AW3" t="n">
-        <v>15.79</v>
+        <v>38.11</v>
       </c>
       <c r="AX3" t="n">
-        <v>16.98</v>
+        <v>29.32</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>14.43</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B4" t="n">
+        <v>19808.5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>35.67</v>
+      </c>
+      <c r="D4" t="n">
+        <v>854.92</v>
+      </c>
+      <c r="E4" t="n">
+        <v>27303</v>
+      </c>
+      <c r="F4" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>155.75</v>
+      </c>
+      <c r="H4" t="n">
+        <v>489.04</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3304.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2863.04</v>
+      </c>
+      <c r="K4" t="n">
+        <v>873.46</v>
+      </c>
+      <c r="M4" t="n">
+        <v>11501.16</v>
+      </c>
+      <c r="N4" t="n">
+        <v>17879.38</v>
+      </c>
+      <c r="O4" t="n">
+        <v>67.56</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1604.18</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>11832.46</v>
+      </c>
+      <c r="R4" t="n">
+        <v>39.08</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5032.74</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2233.55</v>
+      </c>
+      <c r="U4" t="n">
+        <v>862.01</v>
+      </c>
+      <c r="V4" t="n">
+        <v>964</v>
+      </c>
+      <c r="W4" t="n">
+        <v>6774</v>
+      </c>
+      <c r="X4" t="n">
+        <v>45325</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>8092.89</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1920</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2414</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>115.66</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>27.57</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>36.26</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>144.55</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>37.65</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>18.76</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>19.02</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>35.96</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>40.84</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>29.51</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>38.11</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>29.32</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>14.32</v>
       </c>
     </row>
   </sheetData>
@@ -12800,12 +15508,609 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:BI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="n">
+        <v>10201</v>
+      </c>
+      <c r="C1" t="n">
+        <v>10203</v>
+      </c>
+      <c r="D1" t="n">
+        <v>10204</v>
+      </c>
+      <c r="E1" t="n">
+        <v>10205</v>
+      </c>
+      <c r="F1" t="n">
+        <v>10211</v>
+      </c>
+      <c r="G1" t="n">
+        <v>10212</v>
+      </c>
+      <c r="H1" t="n">
+        <v>10401</v>
+      </c>
+      <c r="I1" t="n">
+        <v>10405</v>
+      </c>
+      <c r="J1" t="n">
+        <v>10501</v>
+      </c>
+      <c r="K1" t="n">
+        <v>10601</v>
+      </c>
+      <c r="L1" t="n">
+        <v>10802</v>
+      </c>
+      <c r="M1" t="n">
+        <v>20101</v>
+      </c>
+      <c r="N1" t="n">
+        <v>20201</v>
+      </c>
+      <c r="O1" t="n">
+        <v>20202</v>
+      </c>
+      <c r="P1" t="n">
+        <v>20501</v>
+      </c>
+      <c r="Q1" t="n">
+        <v>20502</v>
+      </c>
+      <c r="R1" t="n">
+        <v>20503</v>
+      </c>
+      <c r="S1" t="n">
+        <v>20509</v>
+      </c>
+      <c r="T1" t="n">
+        <v>30301</v>
+      </c>
+      <c r="U1" t="n">
+        <v>30302</v>
+      </c>
+      <c r="V1" t="n">
+        <v>30401</v>
+      </c>
+      <c r="W1" t="n">
+        <v>30501</v>
+      </c>
+      <c r="X1" t="n">
+        <v>30502</v>
+      </c>
+      <c r="Y1" t="n">
+        <v>30503</v>
+      </c>
+      <c r="Z1" t="n">
+        <v>30504</v>
+      </c>
+      <c r="AA1" t="n">
+        <v>30802</v>
+      </c>
+      <c r="AB1" t="n">
+        <v>30901</v>
+      </c>
+      <c r="AC1" t="n">
+        <v>31002</v>
+      </c>
+      <c r="AD1" t="n">
+        <v>31201</v>
+      </c>
+      <c r="AE1" t="n">
+        <v>31301</v>
+      </c>
+      <c r="AF1" t="n">
+        <v>50102</v>
+      </c>
+      <c r="AG1" t="n">
+        <v>50103</v>
+      </c>
+      <c r="AH1" t="n">
+        <v>50104</v>
+      </c>
+      <c r="AI1" t="n">
+        <v>50105</v>
+      </c>
+      <c r="AJ1" t="n">
+        <v>50106</v>
+      </c>
+      <c r="AK1" t="n">
+        <v>50108</v>
+      </c>
+      <c r="AL1" t="n">
+        <v>50109</v>
+      </c>
+      <c r="AM1" t="n">
+        <v>50201</v>
+      </c>
+      <c r="AN1" t="n">
+        <v>50202</v>
+      </c>
+      <c r="AO1" t="n">
+        <v>50203</v>
+      </c>
+      <c r="AP1" t="n">
+        <v>50204</v>
+      </c>
+      <c r="AQ1" t="n">
+        <v>50205</v>
+      </c>
+      <c r="AR1" t="n">
+        <v>50206</v>
+      </c>
+      <c r="AS1" t="n">
+        <v>50207</v>
+      </c>
+      <c r="AT1" t="n">
+        <v>50208</v>
+      </c>
+      <c r="AU1" t="n">
+        <v>50209</v>
+      </c>
+      <c r="AV1" t="n">
+        <v>50210</v>
+      </c>
+      <c r="AW1" t="n">
+        <v>50212</v>
+      </c>
+      <c r="AX1" t="n">
+        <v>50213</v>
+      </c>
+      <c r="AY1" t="n">
+        <v>50214</v>
+      </c>
+      <c r="AZ1" t="n">
+        <v>50301</v>
+      </c>
+      <c r="BA1" t="n">
+        <v>50302</v>
+      </c>
+      <c r="BB1" t="n">
+        <v>50303</v>
+      </c>
+      <c r="BC1" t="n">
+        <v>50304</v>
+      </c>
+      <c r="BD1" t="n">
+        <v>50305</v>
+      </c>
+      <c r="BE1" t="n">
+        <v>50306</v>
+      </c>
+      <c r="BF1" t="n">
+        <v>50307</v>
+      </c>
+      <c r="BG1" t="n">
+        <v>50308</v>
+      </c>
+      <c r="BH1" t="n">
+        <v>50309</v>
+      </c>
+      <c r="BI1" t="n">
+        <v>50310</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B2" t="n">
+        <v>244.33</v>
+      </c>
+      <c r="E2" t="n">
+        <v>159.01</v>
+      </c>
+      <c r="H2" t="n">
+        <v>141.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>151</v>
+      </c>
+      <c r="J2" t="n">
+        <v>84.36</v>
+      </c>
+      <c r="K2" t="n">
+        <v>58.49</v>
+      </c>
+      <c r="M2" t="n">
+        <v>299.93</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1407.34</v>
+      </c>
+      <c r="O2" t="n">
+        <v>273.63</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1001.34</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>747.4</v>
+      </c>
+      <c r="R2" t="n">
+        <v>209.56</v>
+      </c>
+      <c r="S2" t="n">
+        <v>211.47</v>
+      </c>
+      <c r="X2" t="n">
+        <v>228.58</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>38.41</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>246.03</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>140.66</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>16.48</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>17.51</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>12.66</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B3" t="n">
+        <v>244.27</v>
+      </c>
+      <c r="C3" t="n">
+        <v>71.95</v>
+      </c>
+      <c r="D3" t="n">
+        <v>83.23999999999999</v>
+      </c>
+      <c r="E3" t="n">
+        <v>158.93</v>
+      </c>
+      <c r="F3" t="n">
+        <v>22.19</v>
+      </c>
+      <c r="G3" t="n">
+        <v>44.34</v>
+      </c>
+      <c r="H3" t="n">
+        <v>141.45</v>
+      </c>
+      <c r="I3" t="n">
+        <v>150.94</v>
+      </c>
+      <c r="J3" t="n">
+        <v>84.28</v>
+      </c>
+      <c r="K3" t="n">
+        <v>58.37</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="M3" t="n">
+        <v>299.91</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1407.35</v>
+      </c>
+      <c r="O3" t="n">
+        <v>273.63</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1001.29</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>747.02</v>
+      </c>
+      <c r="R3" t="n">
+        <v>209.49</v>
+      </c>
+      <c r="S3" t="n">
+        <v>211.46</v>
+      </c>
+      <c r="T3" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="U3" t="n">
+        <v>74.69</v>
+      </c>
+      <c r="V3" t="n">
+        <v>106.42</v>
+      </c>
+      <c r="X3" t="n">
+        <v>228.38</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>179.77</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>138.96</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>246.03</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>140.64</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>18.27</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>30.49</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>18.17</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>30.59</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>16.98</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B4" t="n">
+        <v>244.16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>71.83</v>
+      </c>
+      <c r="D4" t="n">
+        <v>83.14</v>
+      </c>
+      <c r="E4" t="n">
+        <v>158.83</v>
+      </c>
+      <c r="F4" t="n">
+        <v>22.22</v>
+      </c>
+      <c r="G4" t="n">
+        <v>44.43</v>
+      </c>
+      <c r="H4" t="n">
+        <v>141.4</v>
+      </c>
+      <c r="I4" t="n">
+        <v>150.85</v>
+      </c>
+      <c r="J4" t="n">
+        <v>84.22</v>
+      </c>
+      <c r="K4" t="n">
+        <v>58.31</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="M4" t="n">
+        <v>299.89</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1407.34</v>
+      </c>
+      <c r="O4" t="n">
+        <v>273.46</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1001.17</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>747.09</v>
+      </c>
+      <c r="R4" t="n">
+        <v>208.77</v>
+      </c>
+      <c r="S4" t="n">
+        <v>211.46</v>
+      </c>
+      <c r="T4" t="n">
+        <v>104.01</v>
+      </c>
+      <c r="U4" t="n">
+        <v>74.65000000000001</v>
+      </c>
+      <c r="V4" t="n">
+        <v>106.29</v>
+      </c>
+      <c r="W4" t="n">
+        <v>57.03</v>
+      </c>
+      <c r="X4" t="n">
+        <v>228.18</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>179.81</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>138.95</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>38.41</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>16.29</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>246.04</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>140.61</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>30.47</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>18.17</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>30.59</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>16.96</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
           <t>id</t>
         </is>
       </c>
@@ -13092,37 +16397,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>30502</v>
+        <v>30501</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WRA 30502</t>
+          <t>WRA 30501</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>46304</v>
+        <v>46306</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>30503</v>
+        <v>30502</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>WRA 30503</t>
+          <t>WRA 30502</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>46305</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>30504</v>
+        <v>30503</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>WRA 30504</t>
+          <t>WRA 30503</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
@@ -13131,70 +16436,70 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>30802</v>
+        <v>30504</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>WRA 30802</t>
+          <t>WRA 30504</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>30901</v>
+        <v>30802</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>WRA 30901</t>
-        </is>
+          <t>WRA 30802</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>46304</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>31002</v>
+        <v>30901</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>WRA 31002</t>
+          <t>WRA 30901</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>31201</v>
+        <v>31002</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>WRA 31201</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>46304</v>
+          <t>WRA 31002</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>31301</v>
+        <v>31201</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>WRA 31301</t>
+          <t>WRA 31201</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>46305</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>50102</v>
+        <v>31301</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>WRA 50102</t>
+          <t>WRA 31301</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
@@ -13203,11 +16508,11 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>50103</v>
+        <v>50102</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>WRA 50103</t>
+          <t>WRA 50102</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
@@ -13216,11 +16521,11 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>50104</v>
+        <v>50103</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>WRA 50104</t>
+          <t>WRA 50103</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
@@ -13229,11 +16534,11 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>50105</v>
+        <v>50104</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>WRA 50105</t>
+          <t>WRA 50104</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
@@ -13242,11 +16547,11 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>50106</v>
+        <v>50105</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>WRA 50106</t>
+          <t>WRA 50105</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
@@ -13255,11 +16560,11 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>50108</v>
+        <v>50106</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>WRA 50108</t>
+          <t>WRA 50106</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
@@ -13268,11 +16573,11 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>50109</v>
+        <v>50108</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>WRA 50109</t>
+          <t>WRA 50108</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
@@ -13281,11 +16586,11 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>50201</v>
+        <v>50109</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>WRA 50201</t>
+          <t>WRA 50109</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
@@ -13294,11 +16599,11 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>50202</v>
+        <v>50201</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>WRA 50202</t>
+          <t>WRA 50201</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
@@ -13307,11 +16612,11 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>50203</v>
+        <v>50202</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>WRA 50203</t>
+          <t>WRA 50202</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
@@ -13320,11 +16625,11 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>50204</v>
+        <v>50203</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>WRA 50204</t>
+          <t>WRA 50203</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
@@ -13333,11 +16638,11 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>50205</v>
+        <v>50204</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>WRA 50205</t>
+          <t>WRA 50204</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
@@ -13346,11 +16651,11 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>50206</v>
+        <v>50205</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>WRA 50206</t>
+          <t>WRA 50205</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
@@ -13359,11 +16664,11 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>50207</v>
+        <v>50206</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>WRA 50207</t>
+          <t>WRA 50206</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
@@ -13372,11 +16677,11 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>50208</v>
+        <v>50207</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>WRA 50208</t>
+          <t>WRA 50207</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
@@ -13385,11 +16690,11 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>50209</v>
+        <v>50208</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>WRA 50209</t>
+          <t>WRA 50208</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
@@ -13398,11 +16703,11 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>50210</v>
+        <v>50209</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>WRA 50210</t>
+          <t>WRA 50209</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
@@ -13411,11 +16716,11 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>50212</v>
+        <v>50210</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>WRA 50212</t>
+          <t>WRA 50210</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
@@ -13424,11 +16729,11 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>50213</v>
+        <v>50212</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>WRA 50213</t>
+          <t>WRA 50212</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
@@ -13437,11 +16742,11 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>50214</v>
+        <v>50213</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>WRA 50214</t>
+          <t>WRA 50213</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
@@ -13450,24 +16755,24 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>50301</v>
+        <v>50214</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>WRA 50301</t>
+          <t>WRA 50214</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>50302</v>
+        <v>50301</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>WRA 50302</t>
+          <t>WRA 50301</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
@@ -13476,11 +16781,11 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>50303</v>
+        <v>50302</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>WRA 50303</t>
+          <t>WRA 50302</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
@@ -13489,11 +16794,11 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>50304</v>
+        <v>50303</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>WRA 50304</t>
+          <t>WRA 50303</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
@@ -13502,11 +16807,11 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>50305</v>
+        <v>50304</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>WRA 50305</t>
+          <t>WRA 50304</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
@@ -13515,11 +16820,11 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>50306</v>
+        <v>50305</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>WRA 50306</t>
+          <t>WRA 50305</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
@@ -13528,11 +16833,11 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>50307</v>
+        <v>50306</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>WRA 50307</t>
+          <t>WRA 50306</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
@@ -13541,11 +16846,11 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>50308</v>
+        <v>50307</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>WRA 50308</t>
+          <t>WRA 50307</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
@@ -13554,11 +16859,11 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>50309</v>
+        <v>50308</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>WRA 50309</t>
+          <t>WRA 50308</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
@@ -13567,14 +16872,27 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
+        <v>50309</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>WRA 50309</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
         <v>50310</v>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>WRA 50310</t>
         </is>
       </c>
-      <c r="C60" s="4" t="n">
+      <c r="C61" s="4" t="n">
         <v>46304</v>
       </c>
     </row>
@@ -13589,7 +16907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -13694,6 +17012,32 @@
       </c>
       <c r="H3" t="n">
         <v>80.7437</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B4" t="n">
+        <v>453.25</v>
+      </c>
+      <c r="C4" t="n">
+        <v>273.03</v>
+      </c>
+      <c r="D4" t="n">
+        <v>198.085</v>
+      </c>
+      <c r="E4" t="n">
+        <v>178.7938</v>
+      </c>
+      <c r="F4" t="n">
+        <v>118.3246</v>
+      </c>
+      <c r="G4" t="n">
+        <v>115.0116</v>
+      </c>
+      <c r="H4" t="n">
+        <v>80.9289</v>
       </c>
     </row>
   </sheetData>
@@ -13849,6 +17193,9 @@
           <t>11-Oct</t>
         </is>
       </c>
+      <c r="G12" t="n">
+        <v>45325</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16536,6 +19883,9 @@
           <t>11-Oct</t>
         </is>
       </c>
+      <c r="G12" t="n">
+        <v>27303</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -19223,6 +22573,9 @@
           <t>11-Oct</t>
         </is>
       </c>
+      <c r="G12" t="n">
+        <v>19808.5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -21910,6 +25263,9 @@
           <t>11-Oct</t>
         </is>
       </c>
+      <c r="G12" t="n">
+        <v>17879.38</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -24597,6 +27953,9 @@
           <t>11-Oct</t>
         </is>
       </c>
+      <c r="G12" t="n">
+        <v>11832.46</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -27284,6 +30643,9 @@
           <t>11-Oct</t>
         </is>
       </c>
+      <c r="G12" t="n">
+        <v>11501.16</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -29951,9 +33313,6 @@
           <t>09-Oct</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>5034.81</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -29962,7 +33321,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>5032.74</v>
+        <v>8074.37</v>
       </c>
     </row>
     <row r="12">
@@ -29970,6 +33329,9 @@
         <is>
           <t>11-Oct</t>
         </is>
+      </c>
+      <c r="G12" t="n">
+        <v>8092.89</v>
       </c>
     </row>
     <row r="13">

--- a/output/Data and Chart Outputs/taiwan_reservoirs_daily.xlsx
+++ b/output/Data and Chart Outputs/taiwan_reservoirs_daily.xlsx
@@ -205,12 +205,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$4</f>
+              <f>'Chart'!$I$2:$I$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$4</f>
+              <f>'Chart'!$B$2:$B$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -241,12 +241,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$4</f>
+              <f>'Chart'!$I$2:$I$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$4</f>
+              <f>'Chart'!$C$2:$C$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -277,12 +277,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$4</f>
+              <f>'Chart'!$I$2:$I$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$4</f>
+              <f>'Chart'!$D$2:$D$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -313,12 +313,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$4</f>
+              <f>'Chart'!$I$2:$I$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$4</f>
+              <f>'Chart'!$E$2:$E$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$4</f>
+              <f>'Chart'!$I$2:$I$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$4</f>
+              <f>'Chart'!$F$2:$F$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -385,12 +385,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$4</f>
+              <f>'Chart'!$I$2:$I$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$4</f>
+              <f>'Chart'!$G$2:$G$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -421,12 +421,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$4</f>
+              <f>'Chart'!$I$2:$I$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$4</f>
+              <f>'Chart'!$H$2:$H$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -526,7 +526,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 10405 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-11</a:t>
+              <a:t>WRA 10405 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-27</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -733,7 +733,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="3330"/>
+          <max val="3370"/>
           <min val="3300"/>
         </scaling>
         <delete val="0"/>
@@ -759,7 +759,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <majorUnit val="5"/>
+        <majorUnit val="10"/>
       </valAx>
       <spPr>
         <a:ln>
@@ -797,7 +797,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 10501 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-11</a:t>
+              <a:t>WRA 10501 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-27</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1004,8 +1004,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2890"/>
-          <min val="2860"/>
+          <max val="2900"/>
+          <min val="2760"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -1030,7 +1030,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <majorUnit val="5"/>
+        <majorUnit val="20"/>
       </valAx>
       <spPr>
         <a:ln>
@@ -1068,7 +1068,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 31201 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-11</a:t>
+              <a:t>WRA 31201 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-27</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1276,7 +1276,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="2420"/>
-          <min val="2414"/>
+          <min val="2350"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -1301,7 +1301,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <majorUnit val="1"/>
+        <majorUnit val="10"/>
       </valAx>
       <spPr>
         <a:ln>
@@ -1339,7 +1339,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 30502 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-11</a:t>
+              <a:t>WRA 30502 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-27</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1546,8 +1546,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46200"/>
-          <min val="45200"/>
+          <max val="46500"/>
+          <min val="44000"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -1572,7 +1572,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <majorUnit val="200"/>
+        <majorUnit val="500"/>
       </valAx>
       <spPr>
         <a:ln>
@@ -1610,7 +1610,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 10205 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-11</a:t>
+              <a:t>WRA 10205 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-27</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1817,8 +1817,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="27450"/>
-          <min val="27300"/>
+          <max val="32000"/>
+          <min val="27000"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -1843,7 +1843,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <majorUnit val="25"/>
+        <majorUnit val="1000"/>
       </valAx>
       <spPr>
         <a:ln>
@@ -1881,7 +1881,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 10201 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-11</a:t>
+              <a:t>WRA 10201 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-27</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2088,7 +2088,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="19975"/>
+          <max val="20600"/>
           <min val="19800"/>
         </scaling>
         <delete val="0"/>
@@ -2114,7 +2114,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <majorUnit val="25"/>
+        <majorUnit val="200"/>
       </valAx>
       <spPr>
         <a:ln>
@@ -2152,7 +2152,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 20201 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-11</a:t>
+              <a:t>WRA 20201 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-27</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2359,8 +2359,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="17884"/>
-          <min val="17879"/>
+          <max val="17900"/>
+          <min val="17400"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -2385,7 +2385,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <majorUnit val="1"/>
+        <majorUnit val="100"/>
       </valAx>
       <spPr>
         <a:ln>
@@ -2423,7 +2423,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 20502 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-11</a:t>
+              <a:t>WRA 20502 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-27</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2630,8 +2630,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="12100"/>
-          <min val="11750"/>
+          <max val="12200"/>
+          <min val="11700"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -2656,7 +2656,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <majorUnit val="50"/>
+        <majorUnit val="100"/>
       </valAx>
       <spPr>
         <a:ln>
@@ -2694,7 +2694,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 20101 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-11</a:t>
+              <a:t>WRA 20101 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-27</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2902,7 +2902,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="11520"/>
-          <min val="11500"/>
+          <min val="11400"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -2927,7 +2927,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <majorUnit val="2.5"/>
+        <majorUnit val="20"/>
       </valAx>
       <spPr>
         <a:ln>
@@ -3236,7 +3236,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 20509 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-11</a:t>
+              <a:t>WRA 20509 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-27</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3443,7 +3443,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="5035"/>
+          <max val="5048"/>
           <min val="5032"/>
         </scaling>
         <delete val="0"/>
@@ -3469,7 +3469,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <majorUnit val="0.5"/>
+        <majorUnit val="2.5"/>
       </valAx>
       <spPr>
         <a:ln>
@@ -4431,6 +4431,9 @@
           <t>27-Oct</t>
         </is>
       </c>
+      <c r="G28" t="n">
+        <v>5047.22</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -7121,6 +7124,9 @@
           <t>27-Oct</t>
         </is>
       </c>
+      <c r="G28" t="n">
+        <v>3365.61</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9811,6 +9817,9 @@
           <t>27-Oct</t>
         </is>
       </c>
+      <c r="G28" t="n">
+        <v>2779.39</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -12501,6 +12510,9 @@
           <t>27-Oct</t>
         </is>
       </c>
+      <c r="G28" t="n">
+        <v>2350</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -14935,7 +14947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI4"/>
+  <dimension ref="A1:BJ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14972,156 +14984,159 @@
         <v>10501</v>
       </c>
       <c r="K1" t="n">
+        <v>10503</v>
+      </c>
+      <c r="L1" t="n">
         <v>10601</v>
       </c>
-      <c r="L1" t="n">
+      <c r="M1" t="n">
         <v>10802</v>
       </c>
-      <c r="M1" t="n">
+      <c r="N1" t="n">
         <v>20101</v>
       </c>
-      <c r="N1" t="n">
+      <c r="O1" t="n">
         <v>20201</v>
       </c>
-      <c r="O1" t="n">
+      <c r="P1" t="n">
         <v>20202</v>
       </c>
-      <c r="P1" t="n">
+      <c r="Q1" t="n">
         <v>20501</v>
       </c>
-      <c r="Q1" t="n">
+      <c r="R1" t="n">
         <v>20502</v>
       </c>
-      <c r="R1" t="n">
+      <c r="S1" t="n">
         <v>20503</v>
       </c>
-      <c r="S1" t="n">
+      <c r="T1" t="n">
         <v>20509</v>
       </c>
-      <c r="T1" t="n">
+      <c r="U1" t="n">
         <v>30301</v>
       </c>
-      <c r="U1" t="n">
+      <c r="V1" t="n">
         <v>30302</v>
       </c>
-      <c r="V1" t="n">
+      <c r="W1" t="n">
         <v>30401</v>
       </c>
-      <c r="W1" t="n">
+      <c r="X1" t="n">
         <v>30501</v>
       </c>
-      <c r="X1" t="n">
+      <c r="Y1" t="n">
         <v>30502</v>
       </c>
-      <c r="Y1" t="n">
+      <c r="Z1" t="n">
         <v>30503</v>
       </c>
-      <c r="Z1" t="n">
+      <c r="AA1" t="n">
         <v>30504</v>
       </c>
-      <c r="AA1" t="n">
+      <c r="AB1" t="n">
         <v>30802</v>
       </c>
-      <c r="AB1" t="n">
+      <c r="AC1" t="n">
         <v>30901</v>
       </c>
-      <c r="AC1" t="n">
+      <c r="AD1" t="n">
         <v>31002</v>
       </c>
-      <c r="AD1" t="n">
+      <c r="AE1" t="n">
         <v>31201</v>
       </c>
-      <c r="AE1" t="n">
+      <c r="AF1" t="n">
         <v>31301</v>
       </c>
-      <c r="AF1" t="n">
+      <c r="AG1" t="n">
         <v>50102</v>
       </c>
-      <c r="AG1" t="n">
+      <c r="AH1" t="n">
         <v>50103</v>
       </c>
-      <c r="AH1" t="n">
+      <c r="AI1" t="n">
         <v>50104</v>
       </c>
-      <c r="AI1" t="n">
+      <c r="AJ1" t="n">
         <v>50105</v>
       </c>
-      <c r="AJ1" t="n">
+      <c r="AK1" t="n">
         <v>50106</v>
       </c>
-      <c r="AK1" t="n">
+      <c r="AL1" t="n">
         <v>50108</v>
       </c>
-      <c r="AL1" t="n">
+      <c r="AM1" t="n">
         <v>50109</v>
       </c>
-      <c r="AM1" t="n">
+      <c r="AN1" t="n">
         <v>50201</v>
       </c>
-      <c r="AN1" t="n">
+      <c r="AO1" t="n">
         <v>50202</v>
       </c>
-      <c r="AO1" t="n">
+      <c r="AP1" t="n">
         <v>50203</v>
       </c>
-      <c r="AP1" t="n">
+      <c r="AQ1" t="n">
         <v>50204</v>
       </c>
-      <c r="AQ1" t="n">
+      <c r="AR1" t="n">
         <v>50205</v>
       </c>
-      <c r="AR1" t="n">
+      <c r="AS1" t="n">
         <v>50206</v>
       </c>
-      <c r="AS1" t="n">
+      <c r="AT1" t="n">
         <v>50207</v>
       </c>
-      <c r="AT1" t="n">
+      <c r="AU1" t="n">
         <v>50208</v>
       </c>
-      <c r="AU1" t="n">
+      <c r="AV1" t="n">
         <v>50209</v>
       </c>
-      <c r="AV1" t="n">
+      <c r="AW1" t="n">
         <v>50210</v>
       </c>
-      <c r="AW1" t="n">
+      <c r="AX1" t="n">
         <v>50212</v>
       </c>
-      <c r="AX1" t="n">
+      <c r="AY1" t="n">
         <v>50213</v>
       </c>
-      <c r="AY1" t="n">
+      <c r="AZ1" t="n">
         <v>50214</v>
       </c>
-      <c r="AZ1" t="n">
+      <c r="BA1" t="n">
         <v>50301</v>
       </c>
-      <c r="BA1" t="n">
+      <c r="BB1" t="n">
         <v>50302</v>
       </c>
-      <c r="BB1" t="n">
+      <c r="BC1" t="n">
         <v>50303</v>
       </c>
-      <c r="BC1" t="n">
+      <c r="BD1" t="n">
         <v>50304</v>
       </c>
-      <c r="BD1" t="n">
+      <c r="BE1" t="n">
         <v>50305</v>
       </c>
-      <c r="BE1" t="n">
+      <c r="BF1" t="n">
         <v>50306</v>
       </c>
-      <c r="BF1" t="n">
+      <c r="BG1" t="n">
         <v>50307</v>
       </c>
-      <c r="BG1" t="n">
+      <c r="BH1" t="n">
         <v>50308</v>
       </c>
-      <c r="BH1" t="n">
+      <c r="BI1" t="n">
         <v>50309</v>
       </c>
-      <c r="BI1" t="n">
+      <c r="BJ1" t="n">
         <v>50310</v>
       </c>
     </row>
@@ -15144,67 +15159,67 @@
       <c r="J2" t="n">
         <v>2887.18</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>897.6799999999999</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>11518.41</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>17879.38</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>74.27</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>1637.13</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>12078.99</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>67.83</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>5034.81</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Y2" t="n">
         <v>46042</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AB2" t="n">
         <v>1920</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AE2" t="n">
         <v>2420</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BA2" t="n">
         <v>2.93</v>
       </c>
-      <c r="BA2" t="n">
+      <c r="BB2" t="n">
         <v>0.42</v>
       </c>
-      <c r="BB2" t="n">
+      <c r="BC2" t="n">
         <v>0.12</v>
       </c>
-      <c r="BC2" t="n">
+      <c r="BD2" t="n">
         <v>1.54</v>
       </c>
-      <c r="BD2" t="n">
+      <c r="BE2" t="n">
         <v>2.4</v>
       </c>
-      <c r="BE2" t="n">
+      <c r="BF2" t="n">
         <v>1.47</v>
       </c>
-      <c r="BF2" t="n">
+      <c r="BG2" t="n">
         <v>0.34</v>
       </c>
-      <c r="BG2" t="n">
+      <c r="BH2" t="n">
         <v>11.42</v>
       </c>
-      <c r="BH2" t="n">
+      <c r="BI2" t="n">
         <v>6.91</v>
       </c>
-      <c r="BI2" t="n">
+      <c r="BJ2" t="n">
         <v>27.63</v>
       </c>
     </row>
@@ -15239,115 +15254,115 @@
       <c r="J3" t="n">
         <v>2873.37</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>881.5</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>11509.78</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>17883.55</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>74.27</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>1627.37</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>11777.04</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>64.73999999999999</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>5032.74</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>2242.67</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>865.14</v>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>984</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Y3" t="n">
         <v>45683</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>8074.37</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AA3" t="n">
         <v>55.09</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AB3" t="n">
         <v>1917</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AE3" t="n">
         <v>2418</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AF3" t="n">
         <v>115.89</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AG3" t="n">
         <v>52.05</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AH3" t="n">
         <v>27.64</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AI3" t="n">
         <v>36.39</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AJ3" t="n">
         <v>23.4</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AK3" t="n">
         <v>21.9</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AL3" t="n">
         <v>4.45</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AM3" t="n">
         <v>0.39</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AN3" t="n">
         <v>145.02</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AO3" t="n">
         <v>37.43</v>
       </c>
-      <c r="AO3" t="n">
+      <c r="AP3" t="n">
         <v>18.87</v>
       </c>
-      <c r="AP3" t="n">
+      <c r="AQ3" t="n">
         <v>19.02</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AR3" t="n">
         <v>35.96</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="AS3" t="n">
         <v>23.65</v>
       </c>
-      <c r="AS3" t="n">
+      <c r="AT3" t="n">
         <v>40.98</v>
       </c>
-      <c r="AT3" t="n">
+      <c r="AU3" t="n">
         <v>5.07</v>
       </c>
-      <c r="AU3" t="n">
+      <c r="AV3" t="n">
         <v>7.66</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AW3" t="n">
         <v>29.51</v>
       </c>
-      <c r="AW3" t="n">
+      <c r="AX3" t="n">
         <v>38.11</v>
       </c>
-      <c r="AX3" t="n">
+      <c r="AY3" t="n">
         <v>29.32</v>
       </c>
-      <c r="AY3" t="n">
+      <c r="AZ3" t="n">
         <v>14.43</v>
       </c>
     </row>
@@ -15382,119 +15397,175 @@
       <c r="J4" t="n">
         <v>2863.04</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>873.46</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>11501.16</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>17879.38</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>67.56</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>1604.18</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>11832.46</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>39.08</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>5032.74</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>2233.55</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>862.01</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>964</v>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>6774</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
         <v>45325</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>8092.89</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
         <v>55</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AB4" t="n">
         <v>1920</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AE4" t="n">
         <v>2414</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AF4" t="n">
         <v>115.66</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AG4" t="n">
         <v>51.7</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AH4" t="n">
         <v>27.57</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AI4" t="n">
         <v>36.26</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AJ4" t="n">
         <v>23.4</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AK4" t="n">
         <v>21.9</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AL4" t="n">
         <v>4.45</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AM4" t="n">
         <v>0.39</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AN4" t="n">
         <v>144.55</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AO4" t="n">
         <v>37.65</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AP4" t="n">
         <v>18.76</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="AQ4" t="n">
         <v>19.02</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AR4" t="n">
         <v>35.96</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="AS4" t="n">
         <v>23.65</v>
       </c>
-      <c r="AS4" t="n">
+      <c r="AT4" t="n">
         <v>40.84</v>
       </c>
-      <c r="AT4" t="n">
+      <c r="AU4" t="n">
         <v>5.07</v>
       </c>
-      <c r="AU4" t="n">
+      <c r="AV4" t="n">
         <v>7.66</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AW4" t="n">
         <v>29.51</v>
       </c>
-      <c r="AW4" t="n">
+      <c r="AX4" t="n">
         <v>38.11</v>
       </c>
-      <c r="AX4" t="n">
+      <c r="AY4" t="n">
         <v>29.32</v>
       </c>
-      <c r="AY4" t="n">
+      <c r="AZ4" t="n">
         <v>14.32</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B5" t="n">
+        <v>20543.41</v>
+      </c>
+      <c r="E5" t="n">
+        <v>31183.36</v>
+      </c>
+      <c r="H5" t="n">
+        <v>403.77</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3365.61</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2779.39</v>
+      </c>
+      <c r="K5" t="n">
+        <v>470.9</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1225.55</v>
+      </c>
+      <c r="N5" t="n">
+        <v>11414.89</v>
+      </c>
+      <c r="O5" t="n">
+        <v>17468.63</v>
+      </c>
+      <c r="P5" t="n">
+        <v>65.63</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>414.69</v>
+      </c>
+      <c r="R5" t="n">
+        <v>12142.89</v>
+      </c>
+      <c r="S5" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="T5" t="n">
+        <v>5047.22</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>44079</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1937</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2350</v>
       </c>
     </row>
   </sheetData>
@@ -15508,7 +15579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI4"/>
+  <dimension ref="A1:BJ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15545,156 +15616,159 @@
         <v>10501</v>
       </c>
       <c r="K1" t="n">
+        <v>10503</v>
+      </c>
+      <c r="L1" t="n">
         <v>10601</v>
       </c>
-      <c r="L1" t="n">
+      <c r="M1" t="n">
         <v>10802</v>
       </c>
-      <c r="M1" t="n">
+      <c r="N1" t="n">
         <v>20101</v>
       </c>
-      <c r="N1" t="n">
+      <c r="O1" t="n">
         <v>20201</v>
       </c>
-      <c r="O1" t="n">
+      <c r="P1" t="n">
         <v>20202</v>
       </c>
-      <c r="P1" t="n">
+      <c r="Q1" t="n">
         <v>20501</v>
       </c>
-      <c r="Q1" t="n">
+      <c r="R1" t="n">
         <v>20502</v>
       </c>
-      <c r="R1" t="n">
+      <c r="S1" t="n">
         <v>20503</v>
       </c>
-      <c r="S1" t="n">
+      <c r="T1" t="n">
         <v>20509</v>
       </c>
-      <c r="T1" t="n">
+      <c r="U1" t="n">
         <v>30301</v>
       </c>
-      <c r="U1" t="n">
+      <c r="V1" t="n">
         <v>30302</v>
       </c>
-      <c r="V1" t="n">
+      <c r="W1" t="n">
         <v>30401</v>
       </c>
-      <c r="W1" t="n">
+      <c r="X1" t="n">
         <v>30501</v>
       </c>
-      <c r="X1" t="n">
+      <c r="Y1" t="n">
         <v>30502</v>
       </c>
-      <c r="Y1" t="n">
+      <c r="Z1" t="n">
         <v>30503</v>
       </c>
-      <c r="Z1" t="n">
+      <c r="AA1" t="n">
         <v>30504</v>
       </c>
-      <c r="AA1" t="n">
+      <c r="AB1" t="n">
         <v>30802</v>
       </c>
-      <c r="AB1" t="n">
+      <c r="AC1" t="n">
         <v>30901</v>
       </c>
-      <c r="AC1" t="n">
+      <c r="AD1" t="n">
         <v>31002</v>
       </c>
-      <c r="AD1" t="n">
+      <c r="AE1" t="n">
         <v>31201</v>
       </c>
-      <c r="AE1" t="n">
+      <c r="AF1" t="n">
         <v>31301</v>
       </c>
-      <c r="AF1" t="n">
+      <c r="AG1" t="n">
         <v>50102</v>
       </c>
-      <c r="AG1" t="n">
+      <c r="AH1" t="n">
         <v>50103</v>
       </c>
-      <c r="AH1" t="n">
+      <c r="AI1" t="n">
         <v>50104</v>
       </c>
-      <c r="AI1" t="n">
+      <c r="AJ1" t="n">
         <v>50105</v>
       </c>
-      <c r="AJ1" t="n">
+      <c r="AK1" t="n">
         <v>50106</v>
       </c>
-      <c r="AK1" t="n">
+      <c r="AL1" t="n">
         <v>50108</v>
       </c>
-      <c r="AL1" t="n">
+      <c r="AM1" t="n">
         <v>50109</v>
       </c>
-      <c r="AM1" t="n">
+      <c r="AN1" t="n">
         <v>50201</v>
       </c>
-      <c r="AN1" t="n">
+      <c r="AO1" t="n">
         <v>50202</v>
       </c>
-      <c r="AO1" t="n">
+      <c r="AP1" t="n">
         <v>50203</v>
       </c>
-      <c r="AP1" t="n">
+      <c r="AQ1" t="n">
         <v>50204</v>
       </c>
-      <c r="AQ1" t="n">
+      <c r="AR1" t="n">
         <v>50205</v>
       </c>
-      <c r="AR1" t="n">
+      <c r="AS1" t="n">
         <v>50206</v>
       </c>
-      <c r="AS1" t="n">
+      <c r="AT1" t="n">
         <v>50207</v>
       </c>
-      <c r="AT1" t="n">
+      <c r="AU1" t="n">
         <v>50208</v>
       </c>
-      <c r="AU1" t="n">
+      <c r="AV1" t="n">
         <v>50209</v>
       </c>
-      <c r="AV1" t="n">
+      <c r="AW1" t="n">
         <v>50210</v>
       </c>
-      <c r="AW1" t="n">
+      <c r="AX1" t="n">
         <v>50212</v>
       </c>
-      <c r="AX1" t="n">
+      <c r="AY1" t="n">
         <v>50213</v>
       </c>
-      <c r="AY1" t="n">
+      <c r="AZ1" t="n">
         <v>50214</v>
       </c>
-      <c r="AZ1" t="n">
+      <c r="BA1" t="n">
         <v>50301</v>
       </c>
-      <c r="BA1" t="n">
+      <c r="BB1" t="n">
         <v>50302</v>
       </c>
-      <c r="BB1" t="n">
+      <c r="BC1" t="n">
         <v>50303</v>
       </c>
-      <c r="BC1" t="n">
+      <c r="BD1" t="n">
         <v>50304</v>
       </c>
-      <c r="BD1" t="n">
+      <c r="BE1" t="n">
         <v>50305</v>
       </c>
-      <c r="BE1" t="n">
+      <c r="BF1" t="n">
         <v>50306</v>
       </c>
-      <c r="BF1" t="n">
+      <c r="BG1" t="n">
         <v>50307</v>
       </c>
-      <c r="BG1" t="n">
+      <c r="BH1" t="n">
         <v>50308</v>
       </c>
-      <c r="BH1" t="n">
+      <c r="BI1" t="n">
         <v>50309</v>
       </c>
-      <c r="BI1" t="n">
+      <c r="BJ1" t="n">
         <v>50310</v>
       </c>
     </row>
@@ -15717,73 +15791,73 @@
       <c r="J2" t="n">
         <v>84.36</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>58.49</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>299.93</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>1407.34</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>273.63</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>1001.34</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>747.4</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>209.56</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>211.47</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Y2" t="n">
         <v>228.58</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AB2" t="n">
         <v>38.41</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AC2" t="n">
         <v>16.31</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AD2" t="n">
         <v>246.03</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AE2" t="n">
         <v>140.66</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BA2" t="n">
         <v>7.93</v>
       </c>
-      <c r="BA2" t="n">
+      <c r="BB2" t="n">
         <v>6.21</v>
       </c>
-      <c r="BB2" t="n">
+      <c r="BC2" t="n">
         <v>3.86</v>
       </c>
-      <c r="BC2" t="n">
+      <c r="BD2" t="n">
         <v>7.6</v>
       </c>
-      <c r="BD2" t="n">
+      <c r="BE2" t="n">
         <v>16.48</v>
       </c>
-      <c r="BE2" t="n">
+      <c r="BF2" t="n">
         <v>13.33</v>
       </c>
-      <c r="BF2" t="n">
+      <c r="BG2" t="n">
         <v>7.73</v>
       </c>
-      <c r="BG2" t="n">
+      <c r="BH2" t="n">
         <v>17.51</v>
       </c>
-      <c r="BH2" t="n">
+      <c r="BI2" t="n">
         <v>17.16</v>
       </c>
-      <c r="BI2" t="n">
+      <c r="BJ2" t="n">
         <v>12.66</v>
       </c>
     </row>
@@ -15818,124 +15892,124 @@
       <c r="J3" t="n">
         <v>84.28</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>58.37</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>4.99</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>299.91</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>1407.35</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>273.63</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>1001.29</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>747.02</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>209.49</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>211.46</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>104.05</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>74.69</v>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>106.42</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Y3" t="n">
         <v>228.38</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>179.77</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AA3" t="n">
         <v>138.96</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AB3" t="n">
         <v>38.4</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AC3" t="n">
         <v>16.3</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AD3" t="n">
         <v>246.03</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AE3" t="n">
         <v>140.64</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AF3" t="n">
         <v>8.779999999999999</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AG3" t="n">
         <v>9.41</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AH3" t="n">
         <v>5.55</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AI3" t="n">
         <v>1.86</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AJ3" t="n">
         <v>12.4</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AK3" t="n">
         <v>23.9</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AL3" t="n">
         <v>7.4</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AM3" t="n">
         <v>3.8</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AN3" t="n">
         <v>18.27</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AO3" t="n">
         <v>5.66</v>
       </c>
-      <c r="AO3" t="n">
+      <c r="AP3" t="n">
         <v>30.49</v>
       </c>
-      <c r="AP3" t="n">
+      <c r="AQ3" t="n">
         <v>18.17</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AR3" t="n">
         <v>3.65</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="AS3" t="n">
         <v>30.59</v>
       </c>
-      <c r="AS3" t="n">
+      <c r="AT3" t="n">
         <v>3.52</v>
       </c>
-      <c r="AT3" t="n">
+      <c r="AU3" t="n">
         <v>8.220000000000001</v>
       </c>
-      <c r="AU3" t="n">
+      <c r="AV3" t="n">
         <v>12.27</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AW3" t="n">
         <v>2.37</v>
       </c>
-      <c r="AW3" t="n">
+      <c r="AX3" t="n">
         <v>2.69</v>
       </c>
-      <c r="AX3" t="n">
+      <c r="AY3" t="n">
         <v>15.79</v>
       </c>
-      <c r="AY3" t="n">
+      <c r="AZ3" t="n">
         <v>16.98</v>
       </c>
     </row>
@@ -15970,128 +16044,190 @@
       <c r="J4" t="n">
         <v>84.22</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>58.31</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>4.97</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>299.89</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>1407.34</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>273.46</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>1001.17</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>747.09</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>208.77</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>211.46</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>104.01</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>74.65000000000001</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>106.29</v>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>57.03</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
         <v>228.18</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>179.81</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
         <v>138.95</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AB4" t="n">
         <v>38.41</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AC4" t="n">
         <v>16.29</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AD4" t="n">
         <v>246.04</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AE4" t="n">
         <v>140.61</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AF4" t="n">
         <v>8.77</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AG4" t="n">
         <v>9.380000000000001</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AH4" t="n">
         <v>5.54</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AI4" t="n">
         <v>1.85</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AJ4" t="n">
         <v>12.4</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AK4" t="n">
         <v>23.9</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AL4" t="n">
         <v>7.4</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AM4" t="n">
         <v>3.8</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AN4" t="n">
         <v>18.26</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AO4" t="n">
         <v>5.67</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AP4" t="n">
         <v>30.47</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="AQ4" t="n">
         <v>18.17</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AR4" t="n">
         <v>3.65</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="AS4" t="n">
         <v>30.59</v>
       </c>
-      <c r="AS4" t="n">
+      <c r="AT4" t="n">
         <v>3.51</v>
       </c>
-      <c r="AT4" t="n">
+      <c r="AU4" t="n">
         <v>8.220000000000001</v>
       </c>
-      <c r="AU4" t="n">
+      <c r="AV4" t="n">
         <v>12.27</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AW4" t="n">
         <v>2.37</v>
       </c>
-      <c r="AW4" t="n">
+      <c r="AX4" t="n">
         <v>2.69</v>
       </c>
-      <c r="AX4" t="n">
+      <c r="AY4" t="n">
         <v>15.79</v>
       </c>
-      <c r="AY4" t="n">
+      <c r="AZ4" t="n">
         <v>16.96</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B5" t="n">
+        <v>245.02</v>
+      </c>
+      <c r="E5" t="n">
+        <v>163.47</v>
+      </c>
+      <c r="H5" t="n">
+        <v>139.87</v>
+      </c>
+      <c r="I5" t="n">
+        <v>151.24</v>
+      </c>
+      <c r="J5" t="n">
+        <v>83.73</v>
+      </c>
+      <c r="K5" t="n">
+        <v>69.27</v>
+      </c>
+      <c r="L5" t="n">
+        <v>60.78</v>
+      </c>
+      <c r="N5" t="n">
+        <v>299.69</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1406.35</v>
+      </c>
+      <c r="P5" t="n">
+        <v>273.41</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>991.67</v>
+      </c>
+      <c r="R5" t="n">
+        <v>747.48</v>
+      </c>
+      <c r="S5" t="n">
+        <v>210.27</v>
+      </c>
+      <c r="T5" t="n">
+        <v>211.53</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>227.48</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>38.46</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>246.03</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>140.13</v>
       </c>
     </row>
   </sheetData>
@@ -16105,7 +16241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16244,47 +16380,47 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10601</v>
+        <v>10503</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WRA 10601</t>
+          <t>WRA 10503</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>46304</v>
+        <v>46322</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>10802</v>
+        <v>10601</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>WRA 10802</t>
-        </is>
+          <t>WRA 10601</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>46304</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>20101</v>
+        <v>10802</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WRA 20101</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>46304</v>
+          <t>WRA 10802</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>20201</v>
+        <v>20101</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WRA 20201</t>
+          <t>WRA 20101</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
@@ -16293,11 +16429,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>20202</v>
+        <v>20201</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WRA 20202</t>
+          <t>WRA 20201</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
@@ -16306,11 +16442,11 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>20501</v>
+        <v>20202</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WRA 20501</t>
+          <t>WRA 20202</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
@@ -16319,11 +16455,11 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>20502</v>
+        <v>20501</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>WRA 20502</t>
+          <t>WRA 20501</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
@@ -16332,11 +16468,11 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20503</v>
+        <v>20502</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>WRA 20503</t>
+          <t>WRA 20502</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
@@ -16345,11 +16481,11 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>20509</v>
+        <v>20503</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>WRA 20509</t>
+          <t>WRA 20503</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
@@ -16358,24 +16494,24 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>30301</v>
+        <v>20509</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>WRA 30301</t>
+          <t>WRA 20509</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>46305</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>30302</v>
+        <v>30301</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WRA 30302</t>
+          <t>WRA 30301</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
@@ -16384,11 +16520,11 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>30401</v>
+        <v>30302</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>WRA 30401</t>
+          <t>WRA 30302</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
@@ -16397,50 +16533,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>30501</v>
+        <v>30401</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WRA 30501</t>
+          <t>WRA 30401</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>46306</v>
+        <v>46305</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>30502</v>
+        <v>30501</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>WRA 30502</t>
+          <t>WRA 30501</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>46304</v>
+        <v>46306</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>30503</v>
+        <v>30502</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>WRA 30503</t>
+          <t>WRA 30502</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>46305</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>30504</v>
+        <v>30503</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>WRA 30504</t>
+          <t>WRA 30503</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
@@ -16449,70 +16585,70 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>30802</v>
+        <v>30504</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>WRA 30802</t>
+          <t>WRA 30504</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>30901</v>
+        <v>30802</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>WRA 30901</t>
-        </is>
+          <t>WRA 30802</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>46304</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>31002</v>
+        <v>30901</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>WRA 31002</t>
+          <t>WRA 30901</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>31201</v>
+        <v>31002</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>WRA 31201</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>46304</v>
+          <t>WRA 31002</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>31301</v>
+        <v>31201</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>WRA 31301</t>
+          <t>WRA 31201</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>46305</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>50102</v>
+        <v>31301</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>WRA 50102</t>
+          <t>WRA 31301</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
@@ -16521,11 +16657,11 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>50103</v>
+        <v>50102</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>WRA 50103</t>
+          <t>WRA 50102</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
@@ -16534,11 +16670,11 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>50104</v>
+        <v>50103</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>WRA 50104</t>
+          <t>WRA 50103</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
@@ -16547,11 +16683,11 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>50105</v>
+        <v>50104</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>WRA 50105</t>
+          <t>WRA 50104</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
@@ -16560,11 +16696,11 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>50106</v>
+        <v>50105</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>WRA 50106</t>
+          <t>WRA 50105</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
@@ -16573,11 +16709,11 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>50108</v>
+        <v>50106</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>WRA 50108</t>
+          <t>WRA 50106</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
@@ -16586,11 +16722,11 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>50109</v>
+        <v>50108</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>WRA 50109</t>
+          <t>WRA 50108</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
@@ -16599,11 +16735,11 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>50201</v>
+        <v>50109</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>WRA 50201</t>
+          <t>WRA 50109</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
@@ -16612,11 +16748,11 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>50202</v>
+        <v>50201</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>WRA 50202</t>
+          <t>WRA 50201</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
@@ -16625,11 +16761,11 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>50203</v>
+        <v>50202</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>WRA 50203</t>
+          <t>WRA 50202</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
@@ -16638,11 +16774,11 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>50204</v>
+        <v>50203</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>WRA 50204</t>
+          <t>WRA 50203</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
@@ -16651,11 +16787,11 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>50205</v>
+        <v>50204</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>WRA 50205</t>
+          <t>WRA 50204</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
@@ -16664,11 +16800,11 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>50206</v>
+        <v>50205</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>WRA 50206</t>
+          <t>WRA 50205</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
@@ -16677,11 +16813,11 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>50207</v>
+        <v>50206</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>WRA 50207</t>
+          <t>WRA 50206</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
@@ -16690,11 +16826,11 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>50208</v>
+        <v>50207</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>WRA 50208</t>
+          <t>WRA 50207</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
@@ -16703,11 +16839,11 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>50209</v>
+        <v>50208</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>WRA 50209</t>
+          <t>WRA 50208</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
@@ -16716,11 +16852,11 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>50210</v>
+        <v>50209</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>WRA 50210</t>
+          <t>WRA 50209</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
@@ -16729,11 +16865,11 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>50212</v>
+        <v>50210</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>WRA 50212</t>
+          <t>WRA 50210</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
@@ -16742,11 +16878,11 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>50213</v>
+        <v>50212</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>WRA 50213</t>
+          <t>WRA 50212</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
@@ -16755,11 +16891,11 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>50214</v>
+        <v>50213</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>WRA 50214</t>
+          <t>WRA 50213</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
@@ -16768,24 +16904,24 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>50301</v>
+        <v>50214</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>WRA 50301</t>
+          <t>WRA 50214</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>50302</v>
+        <v>50301</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>WRA 50302</t>
+          <t>WRA 50301</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
@@ -16794,11 +16930,11 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>50303</v>
+        <v>50302</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>WRA 50303</t>
+          <t>WRA 50302</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
@@ -16807,11 +16943,11 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>50304</v>
+        <v>50303</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>WRA 50304</t>
+          <t>WRA 50303</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
@@ -16820,11 +16956,11 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>50305</v>
+        <v>50304</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>WRA 50305</t>
+          <t>WRA 50304</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
@@ -16833,11 +16969,11 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>50306</v>
+        <v>50305</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>WRA 50306</t>
+          <t>WRA 50305</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
@@ -16846,11 +16982,11 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>50307</v>
+        <v>50306</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>WRA 50307</t>
+          <t>WRA 50306</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
@@ -16859,11 +16995,11 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>50308</v>
+        <v>50307</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>WRA 50308</t>
+          <t>WRA 50307</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
@@ -16872,11 +17008,11 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>50309</v>
+        <v>50308</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>WRA 50309</t>
+          <t>WRA 50308</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
@@ -16885,14 +17021,27 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
+        <v>50309</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>WRA 50309</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
         <v>50310</v>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>WRA 50310</t>
         </is>
       </c>
-      <c r="C61" s="4" t="n">
+      <c r="C62" s="4" t="n">
         <v>46304</v>
       </c>
     </row>
@@ -16907,7 +17056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -17038,6 +17187,29 @@
       </c>
       <c r="H4" t="n">
         <v>80.9289</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B5" t="n">
+        <v>440.79</v>
+      </c>
+      <c r="C5" t="n">
+        <v>311.8336</v>
+      </c>
+      <c r="D5" t="n">
+        <v>205.4341</v>
+      </c>
+      <c r="E5" t="n">
+        <v>174.6863</v>
+      </c>
+      <c r="F5" t="n">
+        <v>121.4289</v>
+      </c>
+      <c r="G5" t="n">
+        <v>114.1489</v>
       </c>
     </row>
   </sheetData>
@@ -17308,6 +17480,9 @@
           <t>27-Oct</t>
         </is>
       </c>
+      <c r="G28" t="n">
+        <v>44079</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -19998,6 +20173,9 @@
           <t>27-Oct</t>
         </is>
       </c>
+      <c r="G28" t="n">
+        <v>31183.36</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -22688,6 +22866,9 @@
           <t>27-Oct</t>
         </is>
       </c>
+      <c r="G28" t="n">
+        <v>20543.41</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -25378,6 +25559,9 @@
           <t>27-Oct</t>
         </is>
       </c>
+      <c r="G28" t="n">
+        <v>17468.63</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -28068,6 +28252,9 @@
           <t>27-Oct</t>
         </is>
       </c>
+      <c r="G28" t="n">
+        <v>12142.89</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -30758,6 +30945,9 @@
           <t>27-Oct</t>
         </is>
       </c>
+      <c r="G28" t="n">
+        <v>11414.89</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">

--- a/output/Data and Chart Outputs/taiwan_reservoirs_daily.xlsx
+++ b/output/Data and Chart Outputs/taiwan_reservoirs_daily.xlsx
@@ -16,13 +16,14 @@
     <sheet name="Water year - WRA 20502" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Water year - WRA 20101" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Water year - WRA 30503" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Water year - WRA 20509" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Water year - WRA 10405" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Water year - WRA 10501" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Water year - WRA 31201" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Daily storage" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Daily level" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Reservoirs" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Water year - WRA 30501" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Water year - WRA 20509" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Water year - WRA 10405" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Water year - WRA 10501" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Water year - WRA 31201" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Daily storage" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Daily level" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Reservoirs" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -205,12 +206,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$5</f>
+              <f>'Chart'!$I$2:$I$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$5</f>
+              <f>'Chart'!$B$2:$B$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -241,12 +242,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$5</f>
+              <f>'Chart'!$I$2:$I$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$5</f>
+              <f>'Chart'!$C$2:$C$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -277,12 +278,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$5</f>
+              <f>'Chart'!$I$2:$I$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$5</f>
+              <f>'Chart'!$D$2:$D$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -313,12 +314,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$5</f>
+              <f>'Chart'!$I$2:$I$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$5</f>
+              <f>'Chart'!$E$2:$E$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -349,12 +350,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$5</f>
+              <f>'Chart'!$I$2:$I$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$5</f>
+              <f>'Chart'!$F$2:$F$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -385,12 +386,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$5</f>
+              <f>'Chart'!$I$2:$I$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$5</f>
+              <f>'Chart'!$G$2:$G$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -421,12 +422,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$5</f>
+              <f>'Chart'!$I$2:$I$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$5</f>
+              <f>'Chart'!$H$2:$H$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -526,7 +527,278 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 10405 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-27</a:t>
+              <a:t>WRA 20509 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-28</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <areaChart>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v> </v>
+          </tx>
+          <spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Water year - WRA 20509'!$H$2:$H$366</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Water year - WRA 20509'!$B$2:$B$366</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>5-year range (2021/22-2025/26)</v>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="AFC6D9"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Water year - WRA 20509'!$H$2:$H$366</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Water year - WRA 20509'!$C$2:$C$366</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </areaChart>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Water year - WRA 20509'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="6E6E6E"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Water year - WRA 20509'!$H$2:$H$366</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Water year - WRA 20509'!$E$2:$E$366</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Water year - WRA 20509'!F1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Water year - WRA 20509'!$H$2:$H$366</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Water year - WRA 20509'!$F$2:$F$366</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Water year - WRA 20509'!G1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="38100">
+              <a:solidFill>
+                <a:srgbClr val="0B3A66"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Water year - WRA 20509'!$H$2:$H$366</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Water year - WRA 20509'!$G$2:$G$366</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="5048"/>
+          <min val="5032"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>million m3</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="0"/>
+        </title>
+        <numFmt formatCode="0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+        <majorUnit val="2.5"/>
+      </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <overlay val="0"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>WRA 10405 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-28</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -733,7 +1005,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="3370"/>
+          <max val="3400"/>
           <min val="3300"/>
         </scaling>
         <delete val="0"/>
@@ -759,7 +1031,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <majorUnit val="10"/>
+        <majorUnit val="20"/>
       </valAx>
       <spPr>
         <a:ln>
@@ -784,7 +1056,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -797,7 +1069,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 10501 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-27</a:t>
+              <a:t>WRA 10501 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-28</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1055,7 +1327,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -1068,7 +1340,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 31201 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-27</a:t>
+              <a:t>WRA 31201 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-28</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1276,7 +1548,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="2420"/>
-          <min val="2350"/>
+          <min val="2340"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -1301,7 +1573,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <majorUnit val="10"/>
+        <majorUnit val="20"/>
       </valAx>
       <spPr>
         <a:ln>
@@ -1339,7 +1611,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 30502 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-27</a:t>
+              <a:t>WRA 30502 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-28</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1547,7 +1819,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="46500"/>
-          <min val="44000"/>
+          <min val="43500"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -1610,7 +1882,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 10205 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-27</a:t>
+              <a:t>WRA 10205 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-28</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1881,7 +2153,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 10201 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-27</a:t>
+              <a:t>WRA 10201 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-28</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2152,7 +2424,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 20201 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-27</a:t>
+              <a:t>WRA 20201 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-28</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2423,7 +2695,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 20502 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-27</a:t>
+              <a:t>WRA 20502 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-28</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2694,7 +2966,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 20101 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-27</a:t>
+              <a:t>WRA 20101 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-28</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2965,7 +3237,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 30503 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-11</a:t>
+              <a:t>WRA 30503 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-28</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3173,7 +3445,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="8095"/>
-          <min val="8070"/>
+          <min val="8065"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -3236,7 +3508,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 20509 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-27</a:t>
+              <a:t>WRA 30501 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-28</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3261,12 +3533,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Water year - WRA 20509'!$H$2:$H$366</f>
+              <f>'Water year - WRA 30501'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Water year - WRA 20509'!$B$2:$B$366</f>
+              <f>'Water year - WRA 30501'!$B$2:$B$366</f>
             </numRef>
           </val>
         </ser>
@@ -3287,12 +3559,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Water year - WRA 20509'!$H$2:$H$366</f>
+              <f>'Water year - WRA 30501'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Water year - WRA 20509'!$C$2:$C$366</f>
+              <f>'Water year - WRA 30501'!$C$2:$C$366</f>
             </numRef>
           </val>
         </ser>
@@ -3306,7 +3578,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Water year - WRA 20509'!E1</f>
+              <f>'Water year - WRA 30501'!E1</f>
             </strRef>
           </tx>
           <spPr>
@@ -3327,12 +3599,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Water year - WRA 20509'!$H$2:$H$366</f>
+              <f>'Water year - WRA 30501'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Water year - WRA 20509'!$E$2:$E$366</f>
+              <f>'Water year - WRA 30501'!$E$2:$E$366</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -3342,7 +3614,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Water year - WRA 20509'!F1</f>
+              <f>'Water year - WRA 30501'!F1</f>
             </strRef>
           </tx>
           <spPr>
@@ -3363,12 +3635,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Water year - WRA 20509'!$H$2:$H$366</f>
+              <f>'Water year - WRA 30501'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Water year - WRA 20509'!$F$2:$F$366</f>
+              <f>'Water year - WRA 30501'!$F$2:$F$366</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -3378,7 +3650,7 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Water year - WRA 20509'!G1</f>
+              <f>'Water year - WRA 30501'!G1</f>
             </strRef>
           </tx>
           <spPr>
@@ -3399,12 +3671,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Water year - WRA 20509'!$H$2:$H$366</f>
+              <f>'Water year - WRA 30501'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Water year - WRA 20509'!$G$2:$G$366</f>
+              <f>'Water year - WRA 30501'!$G$2:$G$366</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -3443,8 +3715,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="5048"/>
-          <min val="5032"/>
+          <max val="6800"/>
+          <min val="6500"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -3469,7 +3741,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <majorUnit val="2.5"/>
+        <majorUnit val="50"/>
       </valAx>
       <spPr>
         <a:ln>
@@ -3576,6 +3848,33 @@
 </file>
 
 <file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9360000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -4296,9 +4595,6 @@
           <t>09-Oct</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>5034.81</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4306,9 +4602,6 @@
           <t>10-Oct</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>5032.74</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4317,7 +4610,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>5032.74</v>
+        <v>6774</v>
       </c>
     </row>
     <row r="13">
@@ -4431,15 +4724,15 @@
           <t>27-Oct</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>5047.22</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
           <t>28-Oct</t>
         </is>
+      </c>
+      <c r="G29" t="n">
+        <v>6529</v>
       </c>
     </row>
     <row r="30">
@@ -6990,7 +7283,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3329.2</v>
+        <v>5034.81</v>
       </c>
     </row>
     <row r="11">
@@ -7000,7 +7293,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3319.18</v>
+        <v>5032.74</v>
       </c>
     </row>
     <row r="12">
@@ -7010,7 +7303,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3304.5</v>
+        <v>5032.74</v>
       </c>
     </row>
     <row r="13">
@@ -7125,7 +7418,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>3365.61</v>
+        <v>5047.22</v>
       </c>
     </row>
     <row r="29">
@@ -7133,6 +7426,9 @@
         <is>
           <t>28-Oct</t>
         </is>
+      </c>
+      <c r="G29" t="n">
+        <v>5045.15</v>
       </c>
     </row>
     <row r="30">
@@ -9683,7 +9979,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2887.18</v>
+        <v>3329.2</v>
       </c>
     </row>
     <row r="11">
@@ -9693,7 +9989,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2873.37</v>
+        <v>3319.18</v>
       </c>
     </row>
     <row r="12">
@@ -9703,7 +9999,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2863.04</v>
+        <v>3304.5</v>
       </c>
     </row>
     <row r="13">
@@ -9818,7 +10114,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2779.39</v>
+        <v>3365.61</v>
       </c>
     </row>
     <row r="29">
@@ -9826,6 +10122,9 @@
         <is>
           <t>28-Oct</t>
         </is>
+      </c>
+      <c r="G29" t="n">
+        <v>3397.94</v>
       </c>
     </row>
     <row r="30">
@@ -12376,7 +12675,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2420</v>
+        <v>2887.18</v>
       </c>
     </row>
     <row r="11">
@@ -12386,7 +12685,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2418</v>
+        <v>2873.37</v>
       </c>
     </row>
     <row r="12">
@@ -12396,7 +12695,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2414</v>
+        <v>2863.04</v>
       </c>
     </row>
     <row r="13">
@@ -12511,7 +12810,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2350</v>
+        <v>2779.39</v>
       </c>
     </row>
     <row r="29">
@@ -12519,6 +12818,9 @@
         <is>
           <t>28-Oct</t>
         </is>
+      </c>
+      <c r="G29" t="n">
+        <v>2816.78</v>
       </c>
     </row>
     <row r="30">
@@ -14947,629 +15249,2693 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ5"/>
+  <dimension ref="A1:H366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B1" t="n">
-        <v>10201</v>
-      </c>
-      <c r="C1" t="n">
-        <v>10203</v>
-      </c>
-      <c r="D1" t="n">
-        <v>10204</v>
-      </c>
-      <c r="E1" t="n">
-        <v>10205</v>
-      </c>
-      <c r="F1" t="n">
-        <v>10211</v>
-      </c>
-      <c r="G1" t="n">
-        <v>10212</v>
-      </c>
-      <c r="H1" t="n">
-        <v>10401</v>
-      </c>
-      <c r="I1" t="n">
-        <v>10405</v>
-      </c>
-      <c r="J1" t="n">
-        <v>10501</v>
-      </c>
-      <c r="K1" t="n">
-        <v>10503</v>
-      </c>
-      <c r="L1" t="n">
-        <v>10601</v>
-      </c>
-      <c r="M1" t="n">
-        <v>10802</v>
-      </c>
-      <c r="N1" t="n">
-        <v>20101</v>
-      </c>
-      <c r="O1" t="n">
-        <v>20201</v>
-      </c>
-      <c r="P1" t="n">
-        <v>20202</v>
-      </c>
-      <c r="Q1" t="n">
-        <v>20501</v>
-      </c>
-      <c r="R1" t="n">
-        <v>20502</v>
-      </c>
-      <c r="S1" t="n">
-        <v>20503</v>
-      </c>
-      <c r="T1" t="n">
-        <v>20509</v>
-      </c>
-      <c r="U1" t="n">
-        <v>30301</v>
-      </c>
-      <c r="V1" t="n">
-        <v>30302</v>
-      </c>
-      <c r="W1" t="n">
-        <v>30401</v>
-      </c>
-      <c r="X1" t="n">
-        <v>30501</v>
-      </c>
-      <c r="Y1" t="n">
-        <v>30502</v>
-      </c>
-      <c r="Z1" t="n">
-        <v>30503</v>
-      </c>
-      <c r="AA1" t="n">
-        <v>30504</v>
-      </c>
-      <c r="AB1" t="n">
-        <v>30802</v>
-      </c>
-      <c r="AC1" t="n">
-        <v>30901</v>
-      </c>
-      <c r="AD1" t="n">
-        <v>31002</v>
-      </c>
-      <c r="AE1" t="n">
-        <v>31201</v>
-      </c>
-      <c r="AF1" t="n">
-        <v>31301</v>
-      </c>
-      <c r="AG1" t="n">
-        <v>50102</v>
-      </c>
-      <c r="AH1" t="n">
-        <v>50103</v>
-      </c>
-      <c r="AI1" t="n">
-        <v>50104</v>
-      </c>
-      <c r="AJ1" t="n">
-        <v>50105</v>
-      </c>
-      <c r="AK1" t="n">
-        <v>50106</v>
-      </c>
-      <c r="AL1" t="n">
-        <v>50108</v>
-      </c>
-      <c r="AM1" t="n">
-        <v>50109</v>
-      </c>
-      <c r="AN1" t="n">
-        <v>50201</v>
-      </c>
-      <c r="AO1" t="n">
-        <v>50202</v>
-      </c>
-      <c r="AP1" t="n">
-        <v>50203</v>
-      </c>
-      <c r="AQ1" t="n">
-        <v>50204</v>
-      </c>
-      <c r="AR1" t="n">
-        <v>50205</v>
-      </c>
-      <c r="AS1" t="n">
-        <v>50206</v>
-      </c>
-      <c r="AT1" t="n">
-        <v>50207</v>
-      </c>
-      <c r="AU1" t="n">
-        <v>50208</v>
-      </c>
-      <c r="AV1" t="n">
-        <v>50209</v>
-      </c>
-      <c r="AW1" t="n">
-        <v>50210</v>
-      </c>
-      <c r="AX1" t="n">
-        <v>50212</v>
-      </c>
-      <c r="AY1" t="n">
-        <v>50213</v>
-      </c>
-      <c r="AZ1" t="n">
-        <v>50214</v>
-      </c>
-      <c r="BA1" t="n">
-        <v>50301</v>
-      </c>
-      <c r="BB1" t="n">
-        <v>50302</v>
-      </c>
-      <c r="BC1" t="n">
-        <v>50303</v>
-      </c>
-      <c r="BD1" t="n">
-        <v>50304</v>
-      </c>
-      <c r="BE1" t="n">
-        <v>50305</v>
-      </c>
-      <c r="BF1" t="n">
-        <v>50306</v>
-      </c>
-      <c r="BG1" t="n">
-        <v>50307</v>
-      </c>
-      <c r="BH1" t="n">
-        <v>50308</v>
-      </c>
-      <c r="BI1" t="n">
-        <v>50309</v>
-      </c>
-      <c r="BJ1" t="n">
-        <v>50310</v>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>5Y min</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>5Y range (max-min)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>5Y max</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>5Y average</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>WY 2025/26</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>WY 2026/27</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Axis label</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n">
-        <v>46304</v>
-      </c>
-      <c r="B2" t="n">
-        <v>19953.65</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27448.98</v>
-      </c>
-      <c r="H2" t="n">
-        <v>494.91</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3329.2</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2887.18</v>
-      </c>
-      <c r="L2" t="n">
-        <v>897.6799999999999</v>
-      </c>
-      <c r="N2" t="n">
-        <v>11518.41</v>
-      </c>
-      <c r="O2" t="n">
-        <v>17879.38</v>
-      </c>
-      <c r="P2" t="n">
-        <v>74.27</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1637.13</v>
-      </c>
-      <c r="R2" t="n">
-        <v>12078.99</v>
-      </c>
-      <c r="S2" t="n">
-        <v>67.83</v>
-      </c>
-      <c r="T2" t="n">
-        <v>5034.81</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>46042</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1920</v>
-      </c>
-      <c r="AE2" t="n">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>01-Oct</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>01-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>02-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>03-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>04-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>05-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>06-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>07-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>08-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>09-Oct</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
         <v>2420</v>
       </c>
-      <c r="BA2" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>11.42</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>6.91</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>27.63</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="n">
-        <v>46305</v>
-      </c>
-      <c r="B3" t="n">
-        <v>19902.41</v>
-      </c>
-      <c r="C3" t="n">
-        <v>36.66</v>
-      </c>
-      <c r="D3" t="n">
-        <v>859.59</v>
-      </c>
-      <c r="E3" t="n">
-        <v>27384.03</v>
-      </c>
-      <c r="F3" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="G3" t="n">
-        <v>149.63</v>
-      </c>
-      <c r="H3" t="n">
-        <v>491.97</v>
-      </c>
-      <c r="I3" t="n">
-        <v>3319.18</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2873.37</v>
-      </c>
-      <c r="L3" t="n">
-        <v>881.5</v>
-      </c>
-      <c r="N3" t="n">
-        <v>11509.78</v>
-      </c>
-      <c r="O3" t="n">
-        <v>17883.55</v>
-      </c>
-      <c r="P3" t="n">
-        <v>74.27</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1627.37</v>
-      </c>
-      <c r="R3" t="n">
-        <v>11777.04</v>
-      </c>
-      <c r="S3" t="n">
-        <v>64.73999999999999</v>
-      </c>
-      <c r="T3" t="n">
-        <v>5032.74</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2242.67</v>
-      </c>
-      <c r="V3" t="n">
-        <v>865.14</v>
-      </c>
-      <c r="W3" t="n">
-        <v>984</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>45683</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>8074.37</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>55.09</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1917</v>
-      </c>
-      <c r="AE3" t="n">
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
         <v>2418</v>
       </c>
-      <c r="AF3" t="n">
-        <v>115.89</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>52.05</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>27.64</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>36.39</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>145.02</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>37.43</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>18.87</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>19.02</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>35.96</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>23.65</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>40.98</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>7.66</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>29.51</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>38.11</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>29.32</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>14.43</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="n">
-        <v>46306</v>
-      </c>
-      <c r="B4" t="n">
-        <v>19808.5</v>
-      </c>
-      <c r="C4" t="n">
-        <v>35.67</v>
-      </c>
-      <c r="D4" t="n">
-        <v>854.92</v>
-      </c>
-      <c r="E4" t="n">
-        <v>27303</v>
-      </c>
-      <c r="F4" t="n">
-        <v>62.3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>155.75</v>
-      </c>
-      <c r="H4" t="n">
-        <v>489.04</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3304.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2863.04</v>
-      </c>
-      <c r="L4" t="n">
-        <v>873.46</v>
-      </c>
-      <c r="N4" t="n">
-        <v>11501.16</v>
-      </c>
-      <c r="O4" t="n">
-        <v>17879.38</v>
-      </c>
-      <c r="P4" t="n">
-        <v>67.56</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1604.18</v>
-      </c>
-      <c r="R4" t="n">
-        <v>11832.46</v>
-      </c>
-      <c r="S4" t="n">
-        <v>39.08</v>
-      </c>
-      <c r="T4" t="n">
-        <v>5032.74</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2233.55</v>
-      </c>
-      <c r="V4" t="n">
-        <v>862.01</v>
-      </c>
-      <c r="W4" t="n">
-        <v>964</v>
-      </c>
-      <c r="X4" t="n">
-        <v>6774</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>45325</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>8092.89</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1920</v>
-      </c>
-      <c r="AE4" t="n">
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>11-Oct</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
         <v>2414</v>
       </c>
-      <c r="AF4" t="n">
-        <v>115.66</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>27.57</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>36.26</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>144.55</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>37.65</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>18.76</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>19.02</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>35.96</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>23.65</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>40.84</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>7.66</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>29.51</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>38.11</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>29.32</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>14.32</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="n">
-        <v>46322</v>
-      </c>
-      <c r="B5" t="n">
-        <v>20543.41</v>
-      </c>
-      <c r="E5" t="n">
-        <v>31183.36</v>
-      </c>
-      <c r="H5" t="n">
-        <v>403.77</v>
-      </c>
-      <c r="I5" t="n">
-        <v>3365.61</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2779.39</v>
-      </c>
-      <c r="K5" t="n">
-        <v>470.9</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1225.55</v>
-      </c>
-      <c r="N5" t="n">
-        <v>11414.89</v>
-      </c>
-      <c r="O5" t="n">
-        <v>17468.63</v>
-      </c>
-      <c r="P5" t="n">
-        <v>65.63</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>414.69</v>
-      </c>
-      <c r="R5" t="n">
-        <v>12142.89</v>
-      </c>
-      <c r="S5" t="n">
-        <v>109.8</v>
-      </c>
-      <c r="T5" t="n">
-        <v>5047.22</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>44079</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1937</v>
-      </c>
-      <c r="AE5" t="n">
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>14-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>15-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>16-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>17-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>18-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>19-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>21-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>22-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>23-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>24-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>25-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>26-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>27-Oct</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
         <v>2350</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>28-Oct</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>2345</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>29-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>30-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>31-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>01-Nov</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>01-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>02-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>03-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>04-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>05-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>06-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>07-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>08-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>09-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>10-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>11-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>12-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>13-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>14-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>15-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>16-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>17-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>18-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>19-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>21-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>22-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>23-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>24-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>25-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>26-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>27-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>28-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>29-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>30-Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>01-Dec</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>01-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>02-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>03-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>04-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>05-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>06-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>07-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>08-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>09-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>10-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>11-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>12-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>13-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>14-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>15-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>16-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>17-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>18-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>19-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>20-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>21-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>22-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>23-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>24-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>25-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>26-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>27-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>28-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>29-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>30-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>31-Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>01-Jan</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>01-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>02-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>03-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>04-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>05-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>06-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>07-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>08-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>09-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>10-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>11-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>12-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>13-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>14-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>15-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>16-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>17-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>18-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>19-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>20-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>21-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>22-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>23-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>24-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>25-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>26-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>27-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>28-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>29-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>30-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>31-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>01-Feb</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>01-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>02-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>03-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>04-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>05-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>06-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>07-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>08-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>09-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>10-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>11-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>12-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>13-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>14-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>15-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>16-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>17-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>18-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>19-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>20-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>21-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>22-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>23-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>24-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>25-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>26-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>27-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>28-Feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>01-Mar</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>01-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>02-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>03-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>04-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>05-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>06-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>07-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>08-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>09-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>10-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>11-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>12-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>13-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>14-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>15-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>16-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>17-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>18-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>19-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>20-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>21-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>22-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>23-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>24-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>25-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>26-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>27-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>28-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>29-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>30-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>31-Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>01-Apr</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>01-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>02-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>03-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>04-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>05-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>06-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>07-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>08-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>09-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>10-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>11-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>12-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>13-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>14-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>15-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>16-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>17-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>18-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>19-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>20-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>21-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>22-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>23-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>24-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>25-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>26-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>27-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>28-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>29-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>30-Apr</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>01-May</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>01-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>02-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>03-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>04-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>05-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>06-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>07-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>08-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>09-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>10-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>11-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>12-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>13-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>14-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>15-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>16-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>17-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>18-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>19-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>20-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>21-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>22-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>23-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>24-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>25-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>26-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>27-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>28-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>29-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>30-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>31-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>01-Jun</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>01-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>02-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>03-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>04-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>05-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>06-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>07-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>08-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>09-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>10-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>11-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>12-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>13-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>14-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>15-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>16-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>17-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>18-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>19-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>20-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>21-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>22-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>23-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>24-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>25-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>26-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>27-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>28-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>29-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>30-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>01-Jul</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>01-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>02-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>03-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>04-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>05-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>06-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>07-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>08-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>09-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>10-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>11-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>12-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>13-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>14-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>15-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>16-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>17-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>18-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>19-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>20-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>21-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>22-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>23-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>24-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>25-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>26-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>27-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>28-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>29-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>30-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>31-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>01-Aug</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>01-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>02-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>03-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>04-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>05-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>06-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>07-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>08-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>09-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>10-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>11-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>12-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>13-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>14-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>15-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>16-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>17-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>18-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>19-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>20-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>21-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>22-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>23-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>24-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>25-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>26-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>27-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>28-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>29-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>30-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>31-Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>01-Sep</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>01-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>02-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>03-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>04-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>05-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>06-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>07-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>08-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>09-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>10-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>11-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>12-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>13-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>14-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>15-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>16-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>17-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>18-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>19-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>20-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>21-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>22-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>23-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>24-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>25-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>26-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>27-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>28-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>29-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>30-Sep</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -15579,7 +17945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ5"/>
+  <dimension ref="A1:BP6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15652,123 +18018,141 @@
         <v>30302</v>
       </c>
       <c r="W1" t="n">
+        <v>30306</v>
+      </c>
+      <c r="X1" t="n">
         <v>30401</v>
       </c>
-      <c r="X1" t="n">
+      <c r="Y1" t="n">
+        <v>30403</v>
+      </c>
+      <c r="Z1" t="n">
         <v>30501</v>
       </c>
-      <c r="Y1" t="n">
+      <c r="AA1" t="n">
         <v>30502</v>
       </c>
-      <c r="Z1" t="n">
+      <c r="AB1" t="n">
         <v>30503</v>
       </c>
-      <c r="AA1" t="n">
+      <c r="AC1" t="n">
         <v>30504</v>
       </c>
-      <c r="AB1" t="n">
+      <c r="AD1" t="n">
+        <v>30601</v>
+      </c>
+      <c r="AE1" t="n">
+        <v>30602</v>
+      </c>
+      <c r="AF1" t="n">
         <v>30802</v>
       </c>
-      <c r="AC1" t="n">
+      <c r="AG1" t="n">
+        <v>30803</v>
+      </c>
+      <c r="AH1" t="n">
         <v>30901</v>
       </c>
-      <c r="AD1" t="n">
+      <c r="AI1" t="n">
         <v>31002</v>
       </c>
-      <c r="AE1" t="n">
+      <c r="AJ1" t="n">
         <v>31201</v>
       </c>
-      <c r="AF1" t="n">
+      <c r="AK1" t="n">
         <v>31301</v>
       </c>
-      <c r="AG1" t="n">
+      <c r="AL1" t="n">
+        <v>40701</v>
+      </c>
+      <c r="AM1" t="n">
         <v>50102</v>
       </c>
-      <c r="AH1" t="n">
+      <c r="AN1" t="n">
         <v>50103</v>
       </c>
-      <c r="AI1" t="n">
+      <c r="AO1" t="n">
         <v>50104</v>
       </c>
-      <c r="AJ1" t="n">
+      <c r="AP1" t="n">
         <v>50105</v>
       </c>
-      <c r="AK1" t="n">
+      <c r="AQ1" t="n">
         <v>50106</v>
       </c>
-      <c r="AL1" t="n">
+      <c r="AR1" t="n">
         <v>50108</v>
       </c>
-      <c r="AM1" t="n">
+      <c r="AS1" t="n">
         <v>50109</v>
       </c>
-      <c r="AN1" t="n">
+      <c r="AT1" t="n">
         <v>50201</v>
       </c>
-      <c r="AO1" t="n">
+      <c r="AU1" t="n">
         <v>50202</v>
       </c>
-      <c r="AP1" t="n">
+      <c r="AV1" t="n">
         <v>50203</v>
       </c>
-      <c r="AQ1" t="n">
+      <c r="AW1" t="n">
         <v>50204</v>
       </c>
-      <c r="AR1" t="n">
+      <c r="AX1" t="n">
         <v>50205</v>
       </c>
-      <c r="AS1" t="n">
+      <c r="AY1" t="n">
         <v>50206</v>
       </c>
-      <c r="AT1" t="n">
+      <c r="AZ1" t="n">
         <v>50207</v>
       </c>
-      <c r="AU1" t="n">
+      <c r="BA1" t="n">
         <v>50208</v>
       </c>
-      <c r="AV1" t="n">
+      <c r="BB1" t="n">
         <v>50209</v>
       </c>
-      <c r="AW1" t="n">
+      <c r="BC1" t="n">
         <v>50210</v>
       </c>
-      <c r="AX1" t="n">
+      <c r="BD1" t="n">
         <v>50212</v>
       </c>
-      <c r="AY1" t="n">
+      <c r="BE1" t="n">
         <v>50213</v>
       </c>
-      <c r="AZ1" t="n">
+      <c r="BF1" t="n">
         <v>50214</v>
       </c>
-      <c r="BA1" t="n">
+      <c r="BG1" t="n">
         <v>50301</v>
       </c>
-      <c r="BB1" t="n">
+      <c r="BH1" t="n">
         <v>50302</v>
       </c>
-      <c r="BC1" t="n">
+      <c r="BI1" t="n">
         <v>50303</v>
       </c>
-      <c r="BD1" t="n">
+      <c r="BJ1" t="n">
         <v>50304</v>
       </c>
-      <c r="BE1" t="n">
+      <c r="BK1" t="n">
         <v>50305</v>
       </c>
-      <c r="BF1" t="n">
+      <c r="BL1" t="n">
         <v>50306</v>
       </c>
-      <c r="BG1" t="n">
+      <c r="BM1" t="n">
         <v>50307</v>
       </c>
-      <c r="BH1" t="n">
+      <c r="BN1" t="n">
         <v>50308</v>
       </c>
-      <c r="BI1" t="n">
+      <c r="BO1" t="n">
         <v>50309</v>
       </c>
-      <c r="BJ1" t="n">
+      <c r="BP1" t="n">
         <v>50310</v>
       </c>
     </row>
@@ -15777,88 +18161,82 @@
         <v>46304</v>
       </c>
       <c r="B2" t="n">
-        <v>244.33</v>
+        <v>19953.65</v>
       </c>
       <c r="E2" t="n">
-        <v>159.01</v>
+        <v>27448.98</v>
       </c>
       <c r="H2" t="n">
-        <v>141.5</v>
+        <v>494.91</v>
       </c>
       <c r="I2" t="n">
-        <v>151</v>
+        <v>3329.2</v>
       </c>
       <c r="J2" t="n">
-        <v>84.36</v>
+        <v>2887.18</v>
       </c>
       <c r="L2" t="n">
-        <v>58.49</v>
+        <v>897.6799999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>299.93</v>
+        <v>11518.41</v>
       </c>
       <c r="O2" t="n">
-        <v>1407.34</v>
+        <v>17879.38</v>
       </c>
       <c r="P2" t="n">
-        <v>273.63</v>
+        <v>74.27</v>
       </c>
       <c r="Q2" t="n">
-        <v>1001.34</v>
+        <v>1637.13</v>
       </c>
       <c r="R2" t="n">
-        <v>747.4</v>
+        <v>12078.99</v>
       </c>
       <c r="S2" t="n">
-        <v>209.56</v>
+        <v>67.83</v>
       </c>
       <c r="T2" t="n">
-        <v>211.47</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>228.58</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>38.41</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>16.31</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>246.03</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>140.66</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>7.93</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>6.21</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>16.48</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>13.33</v>
+        <v>5034.81</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1920</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>2420</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.73</v>
+        <v>2.93</v>
       </c>
       <c r="BH2" t="n">
-        <v>17.51</v>
+        <v>0.42</v>
       </c>
       <c r="BI2" t="n">
-        <v>17.16</v>
+        <v>0.12</v>
       </c>
       <c r="BJ2" t="n">
-        <v>12.66</v>
+        <v>1.54</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>27.63</v>
       </c>
     </row>
     <row r="3">
@@ -15866,151 +18244,142 @@
         <v>46305</v>
       </c>
       <c r="B3" t="n">
-        <v>244.27</v>
+        <v>19902.41</v>
       </c>
       <c r="C3" t="n">
-        <v>71.95</v>
+        <v>36.66</v>
       </c>
       <c r="D3" t="n">
-        <v>83.23999999999999</v>
+        <v>859.59</v>
       </c>
       <c r="E3" t="n">
-        <v>158.93</v>
+        <v>27384.03</v>
       </c>
       <c r="F3" t="n">
-        <v>22.19</v>
+        <v>61.5</v>
       </c>
       <c r="G3" t="n">
-        <v>44.34</v>
+        <v>149.63</v>
       </c>
       <c r="H3" t="n">
-        <v>141.45</v>
+        <v>491.97</v>
       </c>
       <c r="I3" t="n">
-        <v>150.94</v>
+        <v>3319.18</v>
       </c>
       <c r="J3" t="n">
-        <v>84.28</v>
+        <v>2873.37</v>
       </c>
       <c r="L3" t="n">
-        <v>58.37</v>
-      </c>
-      <c r="M3" t="n">
-        <v>4.99</v>
+        <v>881.5</v>
       </c>
       <c r="N3" t="n">
-        <v>299.91</v>
+        <v>11509.78</v>
       </c>
       <c r="O3" t="n">
-        <v>1407.35</v>
+        <v>17883.55</v>
       </c>
       <c r="P3" t="n">
-        <v>273.63</v>
+        <v>74.27</v>
       </c>
       <c r="Q3" t="n">
-        <v>1001.29</v>
+        <v>1627.37</v>
       </c>
       <c r="R3" t="n">
-        <v>747.02</v>
+        <v>11777.04</v>
       </c>
       <c r="S3" t="n">
-        <v>209.49</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>211.46</v>
+        <v>5032.74</v>
       </c>
       <c r="U3" t="n">
-        <v>104.05</v>
+        <v>2242.67</v>
       </c>
       <c r="V3" t="n">
-        <v>74.69</v>
-      </c>
-      <c r="W3" t="n">
-        <v>106.42</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>228.38</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>179.77</v>
+        <v>865.14</v>
+      </c>
+      <c r="X3" t="n">
+        <v>984</v>
       </c>
       <c r="AA3" t="n">
-        <v>138.96</v>
+        <v>45683</v>
       </c>
       <c r="AB3" t="n">
-        <v>38.4</v>
+        <v>8074.37</v>
       </c>
       <c r="AC3" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>246.03</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>140.64</v>
+        <v>55.09</v>
       </c>
       <c r="AF3" t="n">
-        <v>8.779999999999999</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>9.41</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1.86</v>
+        <v>1917</v>
       </c>
       <c r="AJ3" t="n">
-        <v>12.4</v>
+        <v>2418</v>
       </c>
       <c r="AK3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>7.4</v>
+        <v>115.89</v>
       </c>
       <c r="AM3" t="n">
-        <v>3.8</v>
+        <v>52.05</v>
       </c>
       <c r="AN3" t="n">
-        <v>18.27</v>
+        <v>27.64</v>
       </c>
       <c r="AO3" t="n">
-        <v>5.66</v>
+        <v>36.39</v>
       </c>
       <c r="AP3" t="n">
-        <v>30.49</v>
+        <v>23.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>18.17</v>
+        <v>21.9</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.65</v>
+        <v>4.45</v>
       </c>
       <c r="AS3" t="n">
-        <v>30.59</v>
+        <v>0.39</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.52</v>
+        <v>145.02</v>
       </c>
       <c r="AU3" t="n">
-        <v>8.220000000000001</v>
+        <v>37.43</v>
       </c>
       <c r="AV3" t="n">
-        <v>12.27</v>
+        <v>18.87</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.37</v>
+        <v>19.02</v>
       </c>
       <c r="AX3" t="n">
-        <v>2.69</v>
+        <v>35.96</v>
       </c>
       <c r="AY3" t="n">
-        <v>15.79</v>
+        <v>23.65</v>
       </c>
       <c r="AZ3" t="n">
-        <v>16.98</v>
+        <v>40.98</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>29.51</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>38.11</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>29.32</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>14.43</v>
       </c>
     </row>
     <row r="4">
@@ -16018,154 +18387,145 @@
         <v>46306</v>
       </c>
       <c r="B4" t="n">
-        <v>244.16</v>
+        <v>19808.5</v>
       </c>
       <c r="C4" t="n">
-        <v>71.83</v>
+        <v>35.67</v>
       </c>
       <c r="D4" t="n">
-        <v>83.14</v>
+        <v>854.92</v>
       </c>
       <c r="E4" t="n">
-        <v>158.83</v>
+        <v>27303</v>
       </c>
       <c r="F4" t="n">
-        <v>22.22</v>
+        <v>62.3</v>
       </c>
       <c r="G4" t="n">
-        <v>44.43</v>
+        <v>155.75</v>
       </c>
       <c r="H4" t="n">
-        <v>141.4</v>
+        <v>489.04</v>
       </c>
       <c r="I4" t="n">
-        <v>150.85</v>
+        <v>3304.5</v>
       </c>
       <c r="J4" t="n">
-        <v>84.22</v>
+        <v>2863.04</v>
       </c>
       <c r="L4" t="n">
-        <v>58.31</v>
-      </c>
-      <c r="M4" t="n">
-        <v>4.97</v>
+        <v>873.46</v>
       </c>
       <c r="N4" t="n">
-        <v>299.89</v>
+        <v>11501.16</v>
       </c>
       <c r="O4" t="n">
-        <v>1407.34</v>
+        <v>17879.38</v>
       </c>
       <c r="P4" t="n">
-        <v>273.46</v>
+        <v>67.56</v>
       </c>
       <c r="Q4" t="n">
-        <v>1001.17</v>
+        <v>1604.18</v>
       </c>
       <c r="R4" t="n">
-        <v>747.09</v>
+        <v>11832.46</v>
       </c>
       <c r="S4" t="n">
-        <v>208.77</v>
+        <v>39.08</v>
       </c>
       <c r="T4" t="n">
-        <v>211.46</v>
+        <v>5032.74</v>
       </c>
       <c r="U4" t="n">
-        <v>104.01</v>
+        <v>2233.55</v>
       </c>
       <c r="V4" t="n">
-        <v>74.65000000000001</v>
-      </c>
-      <c r="W4" t="n">
-        <v>106.29</v>
+        <v>862.01</v>
       </c>
       <c r="X4" t="n">
-        <v>57.03</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>228.18</v>
+        <v>964</v>
       </c>
       <c r="Z4" t="n">
-        <v>179.81</v>
+        <v>6774</v>
       </c>
       <c r="AA4" t="n">
-        <v>138.95</v>
+        <v>45325</v>
       </c>
       <c r="AB4" t="n">
-        <v>38.41</v>
+        <v>8092.89</v>
       </c>
       <c r="AC4" t="n">
-        <v>16.29</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>246.04</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>140.61</v>
+        <v>55</v>
       </c>
       <c r="AF4" t="n">
-        <v>8.77</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>9.380000000000001</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>5.54</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1.85</v>
+        <v>1920</v>
       </c>
       <c r="AJ4" t="n">
-        <v>12.4</v>
+        <v>2414</v>
       </c>
       <c r="AK4" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>7.4</v>
+        <v>115.66</v>
       </c>
       <c r="AM4" t="n">
-        <v>3.8</v>
+        <v>51.7</v>
       </c>
       <c r="AN4" t="n">
-        <v>18.26</v>
+        <v>27.57</v>
       </c>
       <c r="AO4" t="n">
-        <v>5.67</v>
+        <v>36.26</v>
       </c>
       <c r="AP4" t="n">
-        <v>30.47</v>
+        <v>23.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>18.17</v>
+        <v>21.9</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.65</v>
+        <v>4.45</v>
       </c>
       <c r="AS4" t="n">
-        <v>30.59</v>
+        <v>0.39</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.51</v>
+        <v>144.55</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.220000000000001</v>
+        <v>37.65</v>
       </c>
       <c r="AV4" t="n">
-        <v>12.27</v>
+        <v>18.76</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.37</v>
+        <v>19.02</v>
       </c>
       <c r="AX4" t="n">
-        <v>2.69</v>
+        <v>35.96</v>
       </c>
       <c r="AY4" t="n">
-        <v>15.79</v>
+        <v>23.65</v>
       </c>
       <c r="AZ4" t="n">
-        <v>16.96</v>
+        <v>40.84</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>29.51</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>38.11</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>29.32</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>14.32</v>
       </c>
     </row>
     <row r="5">
@@ -16173,61 +18533,252 @@
         <v>46322</v>
       </c>
       <c r="B5" t="n">
-        <v>245.02</v>
+        <v>20543.41</v>
       </c>
       <c r="E5" t="n">
-        <v>163.47</v>
+        <v>31183.36</v>
       </c>
       <c r="H5" t="n">
-        <v>139.87</v>
+        <v>403.77</v>
       </c>
       <c r="I5" t="n">
-        <v>151.24</v>
+        <v>3365.61</v>
       </c>
       <c r="J5" t="n">
-        <v>83.73</v>
+        <v>2779.39</v>
       </c>
       <c r="K5" t="n">
-        <v>69.27</v>
+        <v>470.9</v>
       </c>
       <c r="L5" t="n">
-        <v>60.78</v>
+        <v>1225.55</v>
       </c>
       <c r="N5" t="n">
-        <v>299.69</v>
+        <v>11414.89</v>
       </c>
       <c r="O5" t="n">
-        <v>1406.35</v>
+        <v>17468.63</v>
       </c>
       <c r="P5" t="n">
-        <v>273.41</v>
+        <v>65.63</v>
       </c>
       <c r="Q5" t="n">
-        <v>991.67</v>
+        <v>414.69</v>
       </c>
       <c r="R5" t="n">
-        <v>747.48</v>
+        <v>12142.89</v>
       </c>
       <c r="S5" t="n">
-        <v>210.27</v>
+        <v>109.8</v>
       </c>
       <c r="T5" t="n">
-        <v>211.53</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>227.48</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>38.46</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>16.25</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>246.03</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>140.13</v>
+        <v>5047.22</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>44079</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1937</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B6" t="n">
+        <v>20569.42</v>
+      </c>
+      <c r="C6" t="n">
+        <v>36.99</v>
+      </c>
+      <c r="D6" t="n">
+        <v>821.61</v>
+      </c>
+      <c r="E6" t="n">
+        <v>31355.32</v>
+      </c>
+      <c r="F6" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>153.71</v>
+      </c>
+      <c r="H6" t="n">
+        <v>412.87</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3397.94</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2816.78</v>
+      </c>
+      <c r="K6" t="n">
+        <v>472</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1218.02</v>
+      </c>
+      <c r="N6" t="n">
+        <v>11458.02</v>
+      </c>
+      <c r="O6" t="n">
+        <v>17555.48</v>
+      </c>
+      <c r="P6" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>410.33</v>
+      </c>
+      <c r="R6" t="n">
+        <v>12110.93</v>
+      </c>
+      <c r="S6" t="n">
+        <v>70.48</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5045.15</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2231.27</v>
+      </c>
+      <c r="V6" t="n">
+        <v>825.26</v>
+      </c>
+      <c r="W6" t="n">
+        <v>43.93</v>
+      </c>
+      <c r="X6" t="n">
+        <v>876</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>159.68</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>6529</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>43743</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>8065.31</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>54.36</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>105.64</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>17.74</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1930</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>375.22</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>2345</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>110.21</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>45.19</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>26.41</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>36.13</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>140.28</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>36.36</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>17.19</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>19.02</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>35.51</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>39.14</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>27.08</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>38.11</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -16241,12 +18792,898 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:BP6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="n">
+        <v>10201</v>
+      </c>
+      <c r="C1" t="n">
+        <v>10203</v>
+      </c>
+      <c r="D1" t="n">
+        <v>10204</v>
+      </c>
+      <c r="E1" t="n">
+        <v>10205</v>
+      </c>
+      <c r="F1" t="n">
+        <v>10211</v>
+      </c>
+      <c r="G1" t="n">
+        <v>10212</v>
+      </c>
+      <c r="H1" t="n">
+        <v>10401</v>
+      </c>
+      <c r="I1" t="n">
+        <v>10405</v>
+      </c>
+      <c r="J1" t="n">
+        <v>10501</v>
+      </c>
+      <c r="K1" t="n">
+        <v>10503</v>
+      </c>
+      <c r="L1" t="n">
+        <v>10601</v>
+      </c>
+      <c r="M1" t="n">
+        <v>10802</v>
+      </c>
+      <c r="N1" t="n">
+        <v>20101</v>
+      </c>
+      <c r="O1" t="n">
+        <v>20201</v>
+      </c>
+      <c r="P1" t="n">
+        <v>20202</v>
+      </c>
+      <c r="Q1" t="n">
+        <v>20501</v>
+      </c>
+      <c r="R1" t="n">
+        <v>20502</v>
+      </c>
+      <c r="S1" t="n">
+        <v>20503</v>
+      </c>
+      <c r="T1" t="n">
+        <v>20509</v>
+      </c>
+      <c r="U1" t="n">
+        <v>30301</v>
+      </c>
+      <c r="V1" t="n">
+        <v>30302</v>
+      </c>
+      <c r="W1" t="n">
+        <v>30306</v>
+      </c>
+      <c r="X1" t="n">
+        <v>30401</v>
+      </c>
+      <c r="Y1" t="n">
+        <v>30403</v>
+      </c>
+      <c r="Z1" t="n">
+        <v>30501</v>
+      </c>
+      <c r="AA1" t="n">
+        <v>30502</v>
+      </c>
+      <c r="AB1" t="n">
+        <v>30503</v>
+      </c>
+      <c r="AC1" t="n">
+        <v>30504</v>
+      </c>
+      <c r="AD1" t="n">
+        <v>30601</v>
+      </c>
+      <c r="AE1" t="n">
+        <v>30602</v>
+      </c>
+      <c r="AF1" t="n">
+        <v>30802</v>
+      </c>
+      <c r="AG1" t="n">
+        <v>30803</v>
+      </c>
+      <c r="AH1" t="n">
+        <v>30901</v>
+      </c>
+      <c r="AI1" t="n">
+        <v>31002</v>
+      </c>
+      <c r="AJ1" t="n">
+        <v>31201</v>
+      </c>
+      <c r="AK1" t="n">
+        <v>31301</v>
+      </c>
+      <c r="AL1" t="n">
+        <v>40701</v>
+      </c>
+      <c r="AM1" t="n">
+        <v>50102</v>
+      </c>
+      <c r="AN1" t="n">
+        <v>50103</v>
+      </c>
+      <c r="AO1" t="n">
+        <v>50104</v>
+      </c>
+      <c r="AP1" t="n">
+        <v>50105</v>
+      </c>
+      <c r="AQ1" t="n">
+        <v>50106</v>
+      </c>
+      <c r="AR1" t="n">
+        <v>50108</v>
+      </c>
+      <c r="AS1" t="n">
+        <v>50109</v>
+      </c>
+      <c r="AT1" t="n">
+        <v>50201</v>
+      </c>
+      <c r="AU1" t="n">
+        <v>50202</v>
+      </c>
+      <c r="AV1" t="n">
+        <v>50203</v>
+      </c>
+      <c r="AW1" t="n">
+        <v>50204</v>
+      </c>
+      <c r="AX1" t="n">
+        <v>50205</v>
+      </c>
+      <c r="AY1" t="n">
+        <v>50206</v>
+      </c>
+      <c r="AZ1" t="n">
+        <v>50207</v>
+      </c>
+      <c r="BA1" t="n">
+        <v>50208</v>
+      </c>
+      <c r="BB1" t="n">
+        <v>50209</v>
+      </c>
+      <c r="BC1" t="n">
+        <v>50210</v>
+      </c>
+      <c r="BD1" t="n">
+        <v>50212</v>
+      </c>
+      <c r="BE1" t="n">
+        <v>50213</v>
+      </c>
+      <c r="BF1" t="n">
+        <v>50214</v>
+      </c>
+      <c r="BG1" t="n">
+        <v>50301</v>
+      </c>
+      <c r="BH1" t="n">
+        <v>50302</v>
+      </c>
+      <c r="BI1" t="n">
+        <v>50303</v>
+      </c>
+      <c r="BJ1" t="n">
+        <v>50304</v>
+      </c>
+      <c r="BK1" t="n">
+        <v>50305</v>
+      </c>
+      <c r="BL1" t="n">
+        <v>50306</v>
+      </c>
+      <c r="BM1" t="n">
+        <v>50307</v>
+      </c>
+      <c r="BN1" t="n">
+        <v>50308</v>
+      </c>
+      <c r="BO1" t="n">
+        <v>50309</v>
+      </c>
+      <c r="BP1" t="n">
+        <v>50310</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B2" t="n">
+        <v>244.33</v>
+      </c>
+      <c r="E2" t="n">
+        <v>159.01</v>
+      </c>
+      <c r="H2" t="n">
+        <v>141.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>151</v>
+      </c>
+      <c r="J2" t="n">
+        <v>84.36</v>
+      </c>
+      <c r="L2" t="n">
+        <v>58.49</v>
+      </c>
+      <c r="N2" t="n">
+        <v>299.93</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1407.34</v>
+      </c>
+      <c r="P2" t="n">
+        <v>273.63</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1001.34</v>
+      </c>
+      <c r="R2" t="n">
+        <v>747.4</v>
+      </c>
+      <c r="S2" t="n">
+        <v>209.56</v>
+      </c>
+      <c r="T2" t="n">
+        <v>211.47</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>228.58</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>38.41</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>246.03</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>140.66</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>16.48</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>17.51</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>12.66</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B3" t="n">
+        <v>244.27</v>
+      </c>
+      <c r="C3" t="n">
+        <v>71.95</v>
+      </c>
+      <c r="D3" t="n">
+        <v>83.23999999999999</v>
+      </c>
+      <c r="E3" t="n">
+        <v>158.93</v>
+      </c>
+      <c r="F3" t="n">
+        <v>22.19</v>
+      </c>
+      <c r="G3" t="n">
+        <v>44.34</v>
+      </c>
+      <c r="H3" t="n">
+        <v>141.45</v>
+      </c>
+      <c r="I3" t="n">
+        <v>150.94</v>
+      </c>
+      <c r="J3" t="n">
+        <v>84.28</v>
+      </c>
+      <c r="L3" t="n">
+        <v>58.37</v>
+      </c>
+      <c r="M3" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="N3" t="n">
+        <v>299.91</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1407.35</v>
+      </c>
+      <c r="P3" t="n">
+        <v>273.63</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1001.29</v>
+      </c>
+      <c r="R3" t="n">
+        <v>747.02</v>
+      </c>
+      <c r="S3" t="n">
+        <v>209.49</v>
+      </c>
+      <c r="T3" t="n">
+        <v>211.46</v>
+      </c>
+      <c r="U3" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="V3" t="n">
+        <v>74.69</v>
+      </c>
+      <c r="X3" t="n">
+        <v>106.42</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>228.38</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>179.77</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>138.96</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>246.03</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>140.64</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>18.27</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>30.49</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>18.17</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>30.59</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>16.98</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B4" t="n">
+        <v>244.16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>71.83</v>
+      </c>
+      <c r="D4" t="n">
+        <v>83.14</v>
+      </c>
+      <c r="E4" t="n">
+        <v>158.83</v>
+      </c>
+      <c r="F4" t="n">
+        <v>22.22</v>
+      </c>
+      <c r="G4" t="n">
+        <v>44.43</v>
+      </c>
+      <c r="H4" t="n">
+        <v>141.4</v>
+      </c>
+      <c r="I4" t="n">
+        <v>150.85</v>
+      </c>
+      <c r="J4" t="n">
+        <v>84.22</v>
+      </c>
+      <c r="L4" t="n">
+        <v>58.31</v>
+      </c>
+      <c r="M4" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="N4" t="n">
+        <v>299.89</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1407.34</v>
+      </c>
+      <c r="P4" t="n">
+        <v>273.46</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1001.17</v>
+      </c>
+      <c r="R4" t="n">
+        <v>747.09</v>
+      </c>
+      <c r="S4" t="n">
+        <v>208.77</v>
+      </c>
+      <c r="T4" t="n">
+        <v>211.46</v>
+      </c>
+      <c r="U4" t="n">
+        <v>104.01</v>
+      </c>
+      <c r="V4" t="n">
+        <v>74.65000000000001</v>
+      </c>
+      <c r="X4" t="n">
+        <v>106.29</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>57.03</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>228.18</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>179.81</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>138.95</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>38.41</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>16.29</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>246.04</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>140.61</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>30.47</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>18.17</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>30.59</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>16.96</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B5" t="n">
+        <v>245.02</v>
+      </c>
+      <c r="E5" t="n">
+        <v>163.47</v>
+      </c>
+      <c r="H5" t="n">
+        <v>139.87</v>
+      </c>
+      <c r="I5" t="n">
+        <v>151.24</v>
+      </c>
+      <c r="J5" t="n">
+        <v>83.73</v>
+      </c>
+      <c r="K5" t="n">
+        <v>69.27</v>
+      </c>
+      <c r="L5" t="n">
+        <v>60.78</v>
+      </c>
+      <c r="N5" t="n">
+        <v>299.69</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1406.35</v>
+      </c>
+      <c r="P5" t="n">
+        <v>273.41</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>991.67</v>
+      </c>
+      <c r="R5" t="n">
+        <v>747.48</v>
+      </c>
+      <c r="S5" t="n">
+        <v>210.27</v>
+      </c>
+      <c r="T5" t="n">
+        <v>211.53</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>227.48</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>38.46</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>246.03</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>140.13</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B6" t="n">
+        <v>245.05</v>
+      </c>
+      <c r="C6" t="n">
+        <v>71.98999999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>82.42</v>
+      </c>
+      <c r="E6" t="n">
+        <v>163.67</v>
+      </c>
+      <c r="F6" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="G6" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>140.04</v>
+      </c>
+      <c r="I6" t="n">
+        <v>151.46</v>
+      </c>
+      <c r="J6" t="n">
+        <v>83.95</v>
+      </c>
+      <c r="K6" t="n">
+        <v>69.28</v>
+      </c>
+      <c r="L6" t="n">
+        <v>60.73</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="N6" t="n">
+        <v>299.79</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1406.56</v>
+      </c>
+      <c r="P6" t="n">
+        <v>273.43</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>991.62</v>
+      </c>
+      <c r="R6" t="n">
+        <v>747.4400000000001</v>
+      </c>
+      <c r="S6" t="n">
+        <v>209.62</v>
+      </c>
+      <c r="T6" t="n">
+        <v>211.52</v>
+      </c>
+      <c r="U6" t="n">
+        <v>104</v>
+      </c>
+      <c r="V6" t="n">
+        <v>74.18000000000001</v>
+      </c>
+      <c r="W6" t="n">
+        <v>58.52</v>
+      </c>
+      <c r="X6" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>56.76</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>227.29</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>179.75</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>138.88</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>36.34</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>38.44</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>45.06</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>16.26</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>246.03</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>140.09</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>30.21</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>18.17</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>30.59</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>17.33</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>17.44</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>11.92</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
           <t>id</t>
         </is>
       </c>
@@ -16533,187 +19970,187 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>30401</v>
+        <v>30306</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WRA 30401</t>
+          <t>WRA 30306</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>46305</v>
+        <v>46323</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>30501</v>
+        <v>30401</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>WRA 30501</t>
+          <t>WRA 30401</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>46306</v>
+        <v>46305</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>30502</v>
+        <v>30403</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>WRA 30502</t>
+          <t>WRA 30403</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>46304</v>
+        <v>46323</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>30503</v>
+        <v>30501</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>WRA 30503</t>
+          <t>WRA 30501</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>30504</v>
+        <v>30502</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>WRA 30504</t>
+          <t>WRA 30502</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>46305</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>30802</v>
+        <v>30503</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>WRA 30802</t>
+          <t>WRA 30503</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>30901</v>
+        <v>30504</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>WRA 30901</t>
-        </is>
+          <t>WRA 30504</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>46305</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>31002</v>
+        <v>30601</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>WRA 31002</t>
-        </is>
+          <t>WRA 30601</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>46323</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>31201</v>
+        <v>30602</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>WRA 31201</t>
+          <t>WRA 30602</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>46304</v>
+        <v>46323</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>31301</v>
+        <v>30802</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>WRA 31301</t>
+          <t>WRA 30802</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>46305</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>50102</v>
+        <v>30803</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>WRA 50102</t>
+          <t>WRA 30803</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>46305</v>
+        <v>46323</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>50103</v>
+        <v>30901</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>WRA 50103</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>46305</v>
+          <t>WRA 30901</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>50104</v>
+        <v>31002</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>WRA 50104</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>46305</v>
+          <t>WRA 31002</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>50105</v>
+        <v>31201</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>WRA 50105</t>
+          <t>WRA 31201</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>46305</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>50106</v>
+        <v>31301</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>WRA 50106</t>
+          <t>WRA 31301</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
@@ -16722,24 +20159,24 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>50108</v>
+        <v>40701</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>WRA 50108</t>
+          <t>WRA 40701</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>46305</v>
+        <v>46323</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>50109</v>
+        <v>50102</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>WRA 50109</t>
+          <t>WRA 50102</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
@@ -16748,11 +20185,11 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>50201</v>
+        <v>50103</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>WRA 50201</t>
+          <t>WRA 50103</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
@@ -16761,11 +20198,11 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>50202</v>
+        <v>50104</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>WRA 50202</t>
+          <t>WRA 50104</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
@@ -16774,11 +20211,11 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>50203</v>
+        <v>50105</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>WRA 50203</t>
+          <t>WRA 50105</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
@@ -16787,11 +20224,11 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>50204</v>
+        <v>50106</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>WRA 50204</t>
+          <t>WRA 50106</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
@@ -16800,11 +20237,11 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>50205</v>
+        <v>50108</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>WRA 50205</t>
+          <t>WRA 50108</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
@@ -16813,11 +20250,11 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>50206</v>
+        <v>50109</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>WRA 50206</t>
+          <t>WRA 50109</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
@@ -16826,11 +20263,11 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>50207</v>
+        <v>50201</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>WRA 50207</t>
+          <t>WRA 50201</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
@@ -16839,11 +20276,11 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>50208</v>
+        <v>50202</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>WRA 50208</t>
+          <t>WRA 50202</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
@@ -16852,11 +20289,11 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>50209</v>
+        <v>50203</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>WRA 50209</t>
+          <t>WRA 50203</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
@@ -16865,11 +20302,11 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>50210</v>
+        <v>50204</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>WRA 50210</t>
+          <t>WRA 50204</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
@@ -16878,11 +20315,11 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>50212</v>
+        <v>50205</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>WRA 50212</t>
+          <t>WRA 50205</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
@@ -16891,11 +20328,11 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>50213</v>
+        <v>50206</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>WRA 50213</t>
+          <t>WRA 50206</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
@@ -16904,11 +20341,11 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>50214</v>
+        <v>50207</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>WRA 50214</t>
+          <t>WRA 50207</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
@@ -16917,89 +20354,89 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>50301</v>
+        <v>50208</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>WRA 50301</t>
+          <t>WRA 50208</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>50302</v>
+        <v>50209</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>WRA 50302</t>
+          <t>WRA 50209</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>50303</v>
+        <v>50210</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>WRA 50303</t>
+          <t>WRA 50210</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>50304</v>
+        <v>50212</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>WRA 50304</t>
+          <t>WRA 50212</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>50305</v>
+        <v>50213</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>WRA 50305</t>
+          <t>WRA 50213</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>50306</v>
+        <v>50214</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>WRA 50306</t>
+          <t>WRA 50214</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>50307</v>
+        <v>50301</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>WRA 50307</t>
+          <t>WRA 50301</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
@@ -17008,11 +20445,11 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>50308</v>
+        <v>50302</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>WRA 50308</t>
+          <t>WRA 50302</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
@@ -17021,11 +20458,11 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>50309</v>
+        <v>50303</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>WRA 50309</t>
+          <t>WRA 50303</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
@@ -17034,14 +20471,92 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
+        <v>50304</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>WRA 50304</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="n">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>50305</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>WRA 50305</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>50306</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>WRA 50306</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="n">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>50307</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>WRA 50307</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>50308</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>WRA 50308</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="n">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>50309</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>WRA 50309</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
         <v>50310</v>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>WRA 50310</t>
         </is>
       </c>
-      <c r="C62" s="4" t="n">
+      <c r="C68" s="4" t="n">
         <v>46304</v>
       </c>
     </row>
@@ -17056,7 +20571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -17210,6 +20725,32 @@
       </c>
       <c r="G5" t="n">
         <v>114.1489</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B6" t="n">
+        <v>437.43</v>
+      </c>
+      <c r="C6" t="n">
+        <v>313.5532</v>
+      </c>
+      <c r="D6" t="n">
+        <v>205.6942</v>
+      </c>
+      <c r="E6" t="n">
+        <v>175.5548</v>
+      </c>
+      <c r="F6" t="n">
+        <v>121.1093</v>
+      </c>
+      <c r="G6" t="n">
+        <v>114.5802</v>
+      </c>
+      <c r="H6" t="n">
+        <v>80.65310000000001</v>
       </c>
     </row>
   </sheetData>
@@ -17490,6 +21031,9 @@
           <t>28-Oct</t>
         </is>
       </c>
+      <c r="G29" t="n">
+        <v>43743</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -20183,6 +23727,9 @@
           <t>28-Oct</t>
         </is>
       </c>
+      <c r="G29" t="n">
+        <v>31355.32</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -22876,6 +26423,9 @@
           <t>28-Oct</t>
         </is>
       </c>
+      <c r="G29" t="n">
+        <v>20569.42</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -25569,6 +29119,9 @@
           <t>28-Oct</t>
         </is>
       </c>
+      <c r="G29" t="n">
+        <v>17555.48</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -28262,6 +31815,9 @@
           <t>28-Oct</t>
         </is>
       </c>
+      <c r="G29" t="n">
+        <v>12110.93</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -30955,6 +34511,9 @@
           <t>28-Oct</t>
         </is>
       </c>
+      <c r="G29" t="n">
+        <v>11458.02</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -33642,6 +37201,9 @@
           <t>28-Oct</t>
         </is>
       </c>
+      <c r="G29" t="n">
+        <v>8065.31</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">

--- a/output/Data and Chart Outputs/taiwan_reservoirs_daily.xlsx
+++ b/output/Data and Chart Outputs/taiwan_reservoirs_daily.xlsx
@@ -206,12 +206,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$6</f>
+              <f>'Chart'!$I$2:$I$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$6</f>
+              <f>'Chart'!$B$2:$B$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -242,12 +242,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$6</f>
+              <f>'Chart'!$I$2:$I$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$6</f>
+              <f>'Chart'!$C$2:$C$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -278,12 +278,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$6</f>
+              <f>'Chart'!$I$2:$I$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$6</f>
+              <f>'Chart'!$D$2:$D$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -314,12 +314,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$6</f>
+              <f>'Chart'!$I$2:$I$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$6</f>
+              <f>'Chart'!$E$2:$E$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -350,12 +350,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$6</f>
+              <f>'Chart'!$I$2:$I$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$6</f>
+              <f>'Chart'!$F$2:$F$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -386,12 +386,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$6</f>
+              <f>'Chart'!$I$2:$I$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$6</f>
+              <f>'Chart'!$G$2:$G$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -422,12 +422,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$6</f>
+              <f>'Chart'!$I$2:$I$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$6</f>
+              <f>'Chart'!$H$2:$H$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -527,7 +527,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 20509 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-28</a:t>
+              <a:t>WRA 20509 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-29</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -798,7 +798,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 10405 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-28</a:t>
+              <a:t>WRA 10405 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-29</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1069,7 +1069,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 10501 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-28</a:t>
+              <a:t>WRA 10501 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-29</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1340,7 +1340,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 31201 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-28</a:t>
+              <a:t>WRA 31201 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-29</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1611,7 +1611,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 30502 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-28</a:t>
+              <a:t>WRA 30502 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-29</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1819,7 +1819,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="46500"/>
-          <min val="43500"/>
+          <min val="43000"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -1882,7 +1882,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 10205 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-28</a:t>
+              <a:t>WRA 10205 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-29</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2153,7 +2153,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 10201 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-28</a:t>
+              <a:t>WRA 10201 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-29</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2424,7 +2424,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 20201 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-28</a:t>
+              <a:t>WRA 20201 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-29</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2695,7 +2695,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 20502 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-28</a:t>
+              <a:t>WRA 20502 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-29</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2966,7 +2966,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 20101 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-28</a:t>
+              <a:t>WRA 20101 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-29</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3237,7 +3237,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 30503 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-28</a:t>
+              <a:t>WRA 30503 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-29</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3445,7 +3445,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="8095"/>
-          <min val="8065"/>
+          <min val="8060"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -3508,7 +3508,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 30501 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-28</a:t>
+              <a:t>WRA 30501 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-29</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -4741,6 +4741,9 @@
           <t>29-Oct</t>
         </is>
       </c>
+      <c r="G30" t="n">
+        <v>6637</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -7437,6 +7440,9 @@
           <t>29-Oct</t>
         </is>
       </c>
+      <c r="G30" t="n">
+        <v>5045.15</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -10133,6 +10139,9 @@
           <t>29-Oct</t>
         </is>
       </c>
+      <c r="G30" t="n">
+        <v>3394.21</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -12829,6 +12838,9 @@
           <t>29-Oct</t>
         </is>
       </c>
+      <c r="G30" t="n">
+        <v>2859.6</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -15525,6 +15537,9 @@
           <t>29-Oct</t>
         </is>
       </c>
+      <c r="G30" t="n">
+        <v>2341</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -17945,7 +17960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP6"/>
+  <dimension ref="A1:BP7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18779,6 +18794,179 @@
       </c>
       <c r="BP6" t="n">
         <v>25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B7" t="n">
+        <v>20586.79</v>
+      </c>
+      <c r="C7" t="n">
+        <v>36.25</v>
+      </c>
+      <c r="D7" t="n">
+        <v>823.9</v>
+      </c>
+      <c r="E7" t="n">
+        <v>31484.57</v>
+      </c>
+      <c r="F7" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>149.63</v>
+      </c>
+      <c r="H7" t="n">
+        <v>425.87</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3394.21</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2859.6</v>
+      </c>
+      <c r="K7" t="n">
+        <v>466.48</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1210.51</v>
+      </c>
+      <c r="N7" t="n">
+        <v>11492.53</v>
+      </c>
+      <c r="O7" t="n">
+        <v>17663.22</v>
+      </c>
+      <c r="P7" t="n">
+        <v>67.18000000000001</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>421.68</v>
+      </c>
+      <c r="R7" t="n">
+        <v>12047.08</v>
+      </c>
+      <c r="S7" t="n">
+        <v>61.65</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5045.15</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2233.55</v>
+      </c>
+      <c r="V7" t="n">
+        <v>829.95</v>
+      </c>
+      <c r="W7" t="n">
+        <v>43.93</v>
+      </c>
+      <c r="X7" t="n">
+        <v>874</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>157</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>6637</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>43389</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>8062.1</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>54.27</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>106.39</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1924</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>370.53</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>2341</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>139.79</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>35.53</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>17.08</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>19.02</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>35.37</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>38.99</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>38.11</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>24.82</v>
       </c>
     </row>
   </sheetData>
@@ -18792,7 +18980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP6"/>
+  <dimension ref="A1:BP7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19665,6 +19853,188 @@
       </c>
       <c r="BP6" t="n">
         <v>11.92</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B7" t="n">
+        <v>245.07</v>
+      </c>
+      <c r="C7" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>82.47</v>
+      </c>
+      <c r="E7" t="n">
+        <v>163.82</v>
+      </c>
+      <c r="F7" t="n">
+        <v>22.22</v>
+      </c>
+      <c r="G7" t="n">
+        <v>44.34</v>
+      </c>
+      <c r="H7" t="n">
+        <v>140.28</v>
+      </c>
+      <c r="I7" t="n">
+        <v>151.45</v>
+      </c>
+      <c r="J7" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>69.23</v>
+      </c>
+      <c r="L7" t="n">
+        <v>60.68</v>
+      </c>
+      <c r="M7" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="N7" t="n">
+        <v>299.87</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1406.82</v>
+      </c>
+      <c r="P7" t="n">
+        <v>273.45</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>991.75</v>
+      </c>
+      <c r="R7" t="n">
+        <v>747.36</v>
+      </c>
+      <c r="S7" t="n">
+        <v>209.42</v>
+      </c>
+      <c r="T7" t="n">
+        <v>211.52</v>
+      </c>
+      <c r="U7" t="n">
+        <v>104.01</v>
+      </c>
+      <c r="V7" t="n">
+        <v>74.23999999999999</v>
+      </c>
+      <c r="W7" t="n">
+        <v>58.52</v>
+      </c>
+      <c r="X7" t="n">
+        <v>105.69</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>56.88</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>227.09</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>179.75</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>138.87</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>36.37</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>38.42</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>44.97</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>246.03</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>140.06</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>18.13</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>30.19</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>18.17</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>30.59</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>17.44</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>17</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>11.87</v>
       </c>
     </row>
   </sheetData>
@@ -20571,7 +20941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -20751,6 +21121,32 @@
       </c>
       <c r="H6" t="n">
         <v>80.65310000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B7" t="n">
+        <v>433.89</v>
+      </c>
+      <c r="C7" t="n">
+        <v>314.8457</v>
+      </c>
+      <c r="D7" t="n">
+        <v>205.8679</v>
+      </c>
+      <c r="E7" t="n">
+        <v>176.6322</v>
+      </c>
+      <c r="F7" t="n">
+        <v>120.4708</v>
+      </c>
+      <c r="G7" t="n">
+        <v>114.9253</v>
+      </c>
+      <c r="H7" t="n">
+        <v>80.62100000000001</v>
       </c>
     </row>
   </sheetData>
@@ -21041,6 +21437,9 @@
           <t>29-Oct</t>
         </is>
       </c>
+      <c r="G30" t="n">
+        <v>43389</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -23737,6 +24136,9 @@
           <t>29-Oct</t>
         </is>
       </c>
+      <c r="G30" t="n">
+        <v>31484.57</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -26433,6 +26835,9 @@
           <t>29-Oct</t>
         </is>
       </c>
+      <c r="G30" t="n">
+        <v>20586.79</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -29129,6 +29534,9 @@
           <t>29-Oct</t>
         </is>
       </c>
+      <c r="G30" t="n">
+        <v>17663.22</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -31825,6 +32233,9 @@
           <t>29-Oct</t>
         </is>
       </c>
+      <c r="G30" t="n">
+        <v>12047.08</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -34521,6 +34932,9 @@
           <t>29-Oct</t>
         </is>
       </c>
+      <c r="G30" t="n">
+        <v>11492.53</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -37211,6 +37625,9 @@
           <t>29-Oct</t>
         </is>
       </c>
+      <c r="G30" t="n">
+        <v>8062.1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">

--- a/output/Data and Chart Outputs/taiwan_reservoirs_daily.xlsx
+++ b/output/Data and Chart Outputs/taiwan_reservoirs_daily.xlsx
@@ -206,12 +206,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$7</f>
+              <f>'Chart'!$I$2:$I$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$7</f>
+              <f>'Chart'!$B$2:$B$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -242,12 +242,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$7</f>
+              <f>'Chart'!$I$2:$I$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$7</f>
+              <f>'Chart'!$C$2:$C$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -278,12 +278,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$7</f>
+              <f>'Chart'!$I$2:$I$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$7</f>
+              <f>'Chart'!$D$2:$D$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -314,12 +314,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$7</f>
+              <f>'Chart'!$I$2:$I$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$7</f>
+              <f>'Chart'!$E$2:$E$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -350,12 +350,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$7</f>
+              <f>'Chart'!$I$2:$I$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$7</f>
+              <f>'Chart'!$F$2:$F$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -386,12 +386,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$7</f>
+              <f>'Chart'!$I$2:$I$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$7</f>
+              <f>'Chart'!$G$2:$G$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -422,12 +422,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$7</f>
+              <f>'Chart'!$I$2:$I$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$7</f>
+              <f>'Chart'!$H$2:$H$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -527,7 +527,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 20509 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-29</a:t>
+              <a:t>WRA 20509 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-30</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -798,7 +798,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 10405 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-29</a:t>
+              <a:t>WRA 10405 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-30</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1069,7 +1069,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 10501 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-29</a:t>
+              <a:t>WRA 10501 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-30</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1340,7 +1340,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 31201 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-29</a:t>
+              <a:t>WRA 31201 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-30</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1548,7 +1548,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="2420"/>
-          <min val="2340"/>
+          <min val="2320"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -1611,7 +1611,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 30502 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-29</a:t>
+              <a:t>WRA 30502 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-30</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1882,7 +1882,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 10205 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-29</a:t>
+              <a:t>WRA 10205 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-30</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2153,7 +2153,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 10201 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-29</a:t>
+              <a:t>WRA 10201 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-30</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2424,7 +2424,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 20201 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-29</a:t>
+              <a:t>WRA 20201 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-30</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2695,7 +2695,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 20502 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-29</a:t>
+              <a:t>WRA 20502 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-30</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2966,7 +2966,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 20101 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-29</a:t>
+              <a:t>WRA 20101 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-30</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3237,7 +3237,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 30503 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-29</a:t>
+              <a:t>WRA 30503 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-30</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3444,8 +3444,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="8095"/>
-          <min val="8060"/>
+          <max val="8100"/>
+          <min val="8050"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -3470,7 +3470,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <majorUnit val="5"/>
+        <majorUnit val="10"/>
       </valAx>
       <spPr>
         <a:ln>
@@ -3508,7 +3508,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>WRA 30501 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-29</a:t>
+              <a:t>WRA 30501 reservoir storage (Water Resources Agency) - water year (Oct-Sep), data to 2026-10-30</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -4751,6 +4751,9 @@
           <t>30-Oct</t>
         </is>
       </c>
+      <c r="G31" t="n">
+        <v>6755</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -7450,6 +7453,9 @@
           <t>30-Oct</t>
         </is>
       </c>
+      <c r="G31" t="n">
+        <v>5045.15</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -10149,6 +10155,9 @@
           <t>30-Oct</t>
         </is>
       </c>
+      <c r="G31" t="n">
+        <v>3396.54</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -12848,6 +12857,9 @@
           <t>30-Oct</t>
         </is>
       </c>
+      <c r="G31" t="n">
+        <v>2890.63</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -15547,6 +15559,9 @@
           <t>30-Oct</t>
         </is>
       </c>
+      <c r="G31" t="n">
+        <v>2337</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -17960,7 +17975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP7"/>
+  <dimension ref="A1:BP8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18967,6 +18982,179 @@
       </c>
       <c r="BP7" t="n">
         <v>24.82</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B8" t="n">
+        <v>20543.41</v>
+      </c>
+      <c r="C8" t="n">
+        <v>35.02</v>
+      </c>
+      <c r="D8" t="n">
+        <v>825.73</v>
+      </c>
+      <c r="E8" t="n">
+        <v>31588.12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>155.07</v>
+      </c>
+      <c r="H8" t="n">
+        <v>435.74</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3396.54</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2890.63</v>
+      </c>
+      <c r="K8" t="n">
+        <v>465.39</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1200.01</v>
+      </c>
+      <c r="N8" t="n">
+        <v>11514.1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>17754.57</v>
+      </c>
+      <c r="P8" t="n">
+        <v>67.18000000000001</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>424.31</v>
+      </c>
+      <c r="R8" t="n">
+        <v>12182.89</v>
+      </c>
+      <c r="S8" t="n">
+        <v>81.95999999999999</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5045.15</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2235.83</v>
+      </c>
+      <c r="V8" t="n">
+        <v>829.95</v>
+      </c>
+      <c r="W8" t="n">
+        <v>43.79</v>
+      </c>
+      <c r="X8" t="n">
+        <v>871</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>155.21</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>6755</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>43037</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>8055.84</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>54.36</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>18.07</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1917</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>364.34</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>2337</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>139.61</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>35.74</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>19.02</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>35.33</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>38.99</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>27.08</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>38.11</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>24.75</v>
       </c>
     </row>
   </sheetData>
@@ -18980,7 +19168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP7"/>
+  <dimension ref="A1:BP8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20035,6 +20223,188 @@
       </c>
       <c r="BP7" t="n">
         <v>11.87</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B8" t="n">
+        <v>245.02</v>
+      </c>
+      <c r="C8" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="D8" t="n">
+        <v>82.51000000000001</v>
+      </c>
+      <c r="E8" t="n">
+        <v>163.94</v>
+      </c>
+      <c r="F8" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="G8" t="n">
+        <v>44.42</v>
+      </c>
+      <c r="H8" t="n">
+        <v>140.46</v>
+      </c>
+      <c r="I8" t="n">
+        <v>151.46</v>
+      </c>
+      <c r="J8" t="n">
+        <v>84.38</v>
+      </c>
+      <c r="K8" t="n">
+        <v>69.22</v>
+      </c>
+      <c r="L8" t="n">
+        <v>60.61</v>
+      </c>
+      <c r="M8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N8" t="n">
+        <v>299.92</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1407.04</v>
+      </c>
+      <c r="P8" t="n">
+        <v>273.45</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>991.78</v>
+      </c>
+      <c r="R8" t="n">
+        <v>747.53</v>
+      </c>
+      <c r="S8" t="n">
+        <v>209.88</v>
+      </c>
+      <c r="T8" t="n">
+        <v>211.52</v>
+      </c>
+      <c r="U8" t="n">
+        <v>104.02</v>
+      </c>
+      <c r="V8" t="n">
+        <v>74.23999999999999</v>
+      </c>
+      <c r="W8" t="n">
+        <v>58.51</v>
+      </c>
+      <c r="X8" t="n">
+        <v>105.67</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>13.31</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>57.01</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>226.89</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>179.73</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>138.88</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>26.58</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>44.85</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>246.04</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>140.03</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>18.13</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>30.18</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>18.17</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>30.59</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>17.39</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>17.45</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>17</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>11.85</v>
       </c>
     </row>
   </sheetData>
@@ -20941,7 +21311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -21147,6 +21517,32 @@
       </c>
       <c r="H7" t="n">
         <v>80.62100000000001</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B8" t="n">
+        <v>430.37</v>
+      </c>
+      <c r="C8" t="n">
+        <v>315.8812</v>
+      </c>
+      <c r="D8" t="n">
+        <v>205.4341</v>
+      </c>
+      <c r="E8" t="n">
+        <v>177.5457</v>
+      </c>
+      <c r="F8" t="n">
+        <v>121.8289</v>
+      </c>
+      <c r="G8" t="n">
+        <v>115.141</v>
+      </c>
+      <c r="H8" t="n">
+        <v>80.55840000000001</v>
       </c>
     </row>
   </sheetData>
@@ -21447,6 +21843,9 @@
           <t>30-Oct</t>
         </is>
       </c>
+      <c r="G31" t="n">
+        <v>43037</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -24146,6 +24545,9 @@
           <t>30-Oct</t>
         </is>
       </c>
+      <c r="G31" t="n">
+        <v>31588.12</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -26845,6 +27247,9 @@
           <t>30-Oct</t>
         </is>
       </c>
+      <c r="G31" t="n">
+        <v>20543.41</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -29544,6 +29949,9 @@
           <t>30-Oct</t>
         </is>
       </c>
+      <c r="G31" t="n">
+        <v>17754.57</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -32243,6 +32651,9 @@
           <t>30-Oct</t>
         </is>
       </c>
+      <c r="G31" t="n">
+        <v>12182.89</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -34942,6 +35353,9 @@
           <t>30-Oct</t>
         </is>
       </c>
+      <c r="G31" t="n">
+        <v>11514.1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -37635,6 +38049,9 @@
           <t>30-Oct</t>
         </is>
       </c>
+      <c r="G31" t="n">
+        <v>8055.84</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
